--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C710754A-B6D8-E544-BD0D-922BF84A641F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82BE1BA-21B6-F047-9EB0-EA301C30C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-4580" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="23220" yWindow="2940" windowWidth="27240" windowHeight="21520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -283,7 +283,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -344,6 +344,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -358,7 +364,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -453,6 +459,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -968,7 +980,10 @@
         <v>45</v>
       </c>
       <c r="D10" s="2"/>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1">
+        <f>COUNTIF(G10:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
     </row>
@@ -1000,7 +1015,10 @@
         <v>47</v>
       </c>
       <c r="D12" s="4"/>
-      <c r="E12" s="29"/>
+      <c r="E12" s="1">
+        <f>COUNTIF(G12:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F12" s="29"/>
       <c r="G12" s="29"/>
       <c r="H12" s="29"/>
@@ -1080,7 +1098,10 @@
         <v>49</v>
       </c>
       <c r="D15" s="4"/>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <f>COUNTIF(G15:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1088,6 +1109,9 @@
       <c r="S15" s="33">
         <v>1</v>
       </c>
+      <c r="T15" s="37">
+        <v>4</v>
+      </c>
     </row>
     <row r="16" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B16" s="1">
@@ -1099,15 +1123,18 @@
       <c r="D16" s="3"/>
       <c r="E16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
       <c r="P16" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T16" s="37">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="17" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1131,7 +1158,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1139,13 +1166,16 @@
         <v>50</v>
       </c>
       <c r="D18" s="4"/>
-      <c r="E18" s="1"/>
+      <c r="E18" s="1">
+        <f>COUNTIF(G18:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1165,7 +1195,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1182,7 +1212,7 @@
       <c r="H20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1201,7 +1231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1209,13 +1239,16 @@
         <v>55</v>
       </c>
       <c r="D22" s="4"/>
-      <c r="E22" s="1"/>
+      <c r="E22" s="1">
+        <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1228,7 +1261,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1250,7 +1283,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1258,13 +1291,16 @@
         <v>53</v>
       </c>
       <c r="D25" s="4"/>
-      <c r="E25" s="1"/>
+      <c r="E25" s="1">
+        <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
       <c r="H25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1281,7 +1317,7 @@
       <c r="H26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1291,7 +1327,7 @@
       <c r="D27" s="3"/>
       <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N27" s="7">
         <v>3</v>
@@ -1302,8 +1338,11 @@
       <c r="Q27" s="32">
         <v>1</v>
       </c>
-    </row>
-    <row r="28" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T27" s="37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1316,7 +1355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>28</v>
       </c>
@@ -1324,11 +1363,14 @@
         <v>46</v>
       </c>
       <c r="D29" s="2"/>
-      <c r="E29" s="1"/>
+      <c r="E29" s="1">
+        <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>29</v>
       </c>
@@ -1336,13 +1378,19 @@
         <v>56</v>
       </c>
       <c r="D30" s="4"/>
-      <c r="E30" s="1"/>
+      <c r="E30" s="1">
+        <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="R30" s="1"/>
-    </row>
-    <row r="31" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T30" s="37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1351,7 +1399,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="35" t="s">
         <v>35</v>
       </c>
@@ -1516,7 +1564,7 @@
       </c>
       <c r="E40" s="1">
         <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F40" s="1" t="s">
         <v>2</v>
@@ -1538,7 +1586,9 @@
       <c r="Q40" s="29"/>
       <c r="R40" s="5"/>
       <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
+      <c r="T40" s="38">
+        <v>5</v>
+      </c>
       <c r="U40" s="29"/>
       <c r="V40" s="29"/>
       <c r="W40" s="29"/>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E82BE1BA-21B6-F047-9EB0-EA301C30C9E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C487A089-0201-7C43-9D6F-900C1AAFDAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23220" yWindow="2940" windowWidth="27240" windowHeight="21520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10220" yWindow="600" windowWidth="26220" windowHeight="27280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -200,9 +200,6 @@
     <t>Lord I Lift Your Name On High</t>
   </si>
   <si>
-    <t>16s</t>
-  </si>
-  <si>
     <t>I Will Not Forget You</t>
   </si>
   <si>
@@ -210,6 +207,9 @@
   </si>
   <si>
     <t>On the Lord's Day</t>
+  </si>
+  <si>
+    <t>Turn Your Eyes Upon Jesus</t>
   </si>
 </sst>
 </file>
@@ -454,17 +454,17 @@
     <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -685,7 +685,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1016"/>
+  <dimension ref="A1:AD1017"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
@@ -793,10 +793,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="36"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="18"/>
       <c r="E2" s="24"/>
       <c r="F2" s="16"/>
@@ -846,7 +846,7 @@
       <c r="D4" s="3"/>
       <c r="E4" s="1">
         <f>COUNTIF(G4:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
@@ -859,6 +859,9 @@
       <c r="R4" s="1"/>
       <c r="S4" s="33">
         <v>3</v>
+      </c>
+      <c r="U4" s="33">
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1109,7 +1112,7 @@
       <c r="S15" s="33">
         <v>1</v>
       </c>
-      <c r="T15" s="37">
+      <c r="T15" s="35">
         <v>4</v>
       </c>
     </row>
@@ -1130,11 +1133,11 @@
       <c r="P16" s="27">
         <v>1</v>
       </c>
-      <c r="T16" s="37">
+      <c r="T16" s="35">
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1158,7 +1161,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1175,17 +1178,17 @@
       <c r="H18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
-      <c r="C19" s="23" t="s">
+      <c r="C19" s="31" t="s">
         <v>10</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="1">
         <f>COUNTIF(G19:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>2</v>
@@ -1194,8 +1197,11 @@
       <c r="L19" s="8">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U19" s="33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1212,7 +1218,7 @@
       <c r="H20" s="1"/>
       <c r="R20" s="1"/>
     </row>
-    <row r="21" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1222,7 +1228,7 @@
       <c r="D21" s="4"/>
       <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>4</v>
@@ -1230,13 +1236,16 @@
       <c r="G21" s="11">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U21" s="33">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
       <c r="C22" s="31" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D22" s="4"/>
       <c r="E22" s="1">
@@ -1248,7 +1257,7 @@
       <c r="H22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1261,7 +1270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1283,7 +1292,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="25" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1300,12 +1309,12 @@
       <c r="H25" s="1"/>
       <c r="R25" s="1"/>
     </row>
-    <row r="26" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
       <c r="C26" s="31" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D26" s="4"/>
       <c r="E26" s="1">
@@ -1317,7 +1326,7 @@
       <c r="H26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1338,11 +1347,11 @@
       <c r="Q27" s="32">
         <v>1</v>
       </c>
-      <c r="T27" s="37">
+      <c r="T27" s="35">
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1355,7 +1364,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>28</v>
       </c>
@@ -1370,27 +1379,30 @@
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
     </row>
-    <row r="30" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>29</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D30" s="4"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="R30" s="1"/>
-      <c r="T30" s="37">
+      <c r="T30" s="35">
         <v>1</v>
       </c>
-    </row>
-    <row r="31" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="U30" s="33">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1"/>
       <c r="C31" s="2"/>
       <c r="D31" s="2"/>
@@ -1399,11 +1411,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="2:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="35" t="s">
+    <row r="32" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C32" s="36"/>
+      <c r="C32" s="38"/>
       <c r="D32" s="19"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
@@ -1586,7 +1598,7 @@
       <c r="Q40" s="29"/>
       <c r="R40" s="5"/>
       <c r="S40" s="29"/>
-      <c r="T40" s="38">
+      <c r="T40" s="36">
         <v>5</v>
       </c>
       <c r="U40" s="29"/>
@@ -1758,24 +1770,33 @@
       </c>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B48" s="1" t="s">
-        <v>54</v>
+      <c r="B48" s="1">
+        <v>16</v>
       </c>
       <c r="C48" s="31" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
+      <c r="K48" s="22"/>
+      <c r="L48" s="8"/>
+      <c r="U48" s="33">
+        <v>5</v>
+      </c>
     </row>
     <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B49" s="1"/>
-      <c r="C49" s="4"/>
-      <c r="D49" s="4"/>
+      <c r="B49" s="1">
+        <v>17</v>
+      </c>
+      <c r="C49" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="2"/>
       <c r="E49" s="1">
         <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1784,11 +1805,9 @@
       <c r="G49" s="1"/>
     </row>
     <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="35" t="s">
-        <v>36</v>
-      </c>
-      <c r="C50" s="36"/>
-      <c r="D50" s="19"/>
+      <c r="B50" s="1"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="4"/>
       <c r="E50" s="1">
         <f>COUNTIF(G50:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1797,33 +1816,26 @@
       <c r="G50" s="1"/>
     </row>
     <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="1">
-        <v>1</v>
-      </c>
-      <c r="C51" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" s="4"/>
+      <c r="B51" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="38"/>
+      <c r="D51" s="19"/>
       <c r="E51" s="1">
         <f>COUNTIF(G51:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F51" s="1"/>
       <c r="G51" s="1"/>
-      <c r="J51" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B52" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C52" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D52" s="20"/>
+        <v>31</v>
+      </c>
+      <c r="D52" s="4"/>
       <c r="E52" s="1">
         <f>COUNTIF(G52:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1832,14 +1844,29 @@
         <v>2</v>
       </c>
       <c r="G52" s="1"/>
-      <c r="K52" s="22">
+      <c r="J52" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B53" s="1"/>
-      <c r="F53" s="1"/>
+      <c r="B53" s="1">
+        <v>2</v>
+      </c>
+      <c r="C53" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D53" s="20"/>
+      <c r="E53" s="1">
+        <f>COUNTIF(G53:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G53" s="1"/>
+      <c r="K53" s="22">
+        <v>2</v>
+      </c>
     </row>
     <row r="54" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1"/>
@@ -2081,7 +2108,7 @@
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
     </row>
-    <row r="102" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="102" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B102" s="1"/>
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
@@ -6656,21 +6683,26 @@
       <c r="F1016" s="1"/>
       <c r="G1016" s="1"/>
     </row>
+    <row r="1017" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1017" s="1"/>
+      <c r="F1017" s="1"/>
+      <c r="G1017" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:S30">
-    <sortCondition ref="C3:C30"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C33:V49">
+    <sortCondition ref="C33:C49"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B50:C50"/>
+    <mergeCell ref="B51:C51"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C12" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
     <hyperlink ref="C27" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
     <hyperlink ref="C29" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
     <hyperlink ref="C36" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="C48" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="C49" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="C15" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="C18" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
@@ -6688,6 +6720,8 @@
     <hyperlink ref="C26" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
     <hyperlink ref="C16" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
     <hyperlink ref="C22" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
+    <hyperlink ref="C48" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="C19" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C487A089-0201-7C43-9D6F-900C1AAFDAA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E84E3A-1413-8741-AC50-5DD4CBEBFBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10220" yWindow="600" windowWidth="26220" windowHeight="27280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2660" yWindow="600" windowWidth="33320" windowHeight="27280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
   <si>
     <t>Key</t>
   </si>
@@ -210,6 +210,9 @@
   </si>
   <si>
     <t>Turn Your Eyes Upon Jesus</t>
+  </si>
+  <si>
+    <t>Still</t>
   </si>
 </sst>
 </file>
@@ -685,7 +688,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1017"/>
+  <dimension ref="A1:AD1018"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
@@ -1369,445 +1372,451 @@
         <v>28</v>
       </c>
       <c r="C29" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D29" s="2"/>
+        <v>58</v>
+      </c>
+      <c r="D29" s="4"/>
       <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>29</v>
       </c>
       <c r="C30" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="D30" s="4"/>
+        <v>46</v>
+      </c>
+      <c r="D30" s="2"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="T30" s="35">
-        <v>1</v>
-      </c>
-      <c r="U30" s="33">
-        <v>4</v>
-      </c>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1"/>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="B31" s="1">
+        <v>30</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="D31" s="4"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="T31" s="35">
+        <v>1</v>
+      </c>
+      <c r="U31" s="33">
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="38"/>
-      <c r="D32" s="19"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="2"/>
+      <c r="B33" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="38"/>
+      <c r="D33" s="19"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="K33" s="22">
-        <v>5</v>
-      </c>
-      <c r="O33" s="22">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="32">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>2</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="C34" s="23" t="s">
+        <v>32</v>
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="1">
         <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G34" s="1"/>
+      <c r="K34" s="22">
+        <v>5</v>
+      </c>
+      <c r="O34" s="22">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="32">
+        <v>5</v>
+      </c>
     </row>
     <row r="35" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
-        <v>3</v>
-      </c>
-      <c r="C35" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D35" s="2"/>
       <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="I35" s="6">
-        <v>5</v>
-      </c>
-      <c r="P35" s="27">
-        <v>2</v>
-      </c>
     </row>
     <row r="36" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
-        <v>4</v>
-      </c>
-      <c r="C36" s="31" t="s">
-        <v>48</v>
+        <v>3</v>
+      </c>
+      <c r="C36" s="23" t="s">
+        <v>30</v>
       </c>
       <c r="D36" s="4"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="N36" s="7">
+      <c r="I36" s="6">
         <v>5</v>
+      </c>
+      <c r="P36" s="27">
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
-        <v>5</v>
-      </c>
-      <c r="C37" s="23" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>48</v>
       </c>
       <c r="D37" s="4"/>
       <c r="E37" s="1">
         <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="J37" s="8">
-        <v>3</v>
+      <c r="N37" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="23" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="D38" s="4"/>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G38" s="1"/>
       <c r="J38" s="8">
-        <v>5</v>
-      </c>
-      <c r="L38" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q38" s="32">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
+        <v>6</v>
+      </c>
+      <c r="C39" s="23" t="s">
+        <v>41</v>
+      </c>
+      <c r="D39" s="4"/>
+      <c r="E39" s="1">
+        <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="J39" s="8">
+        <v>5</v>
+      </c>
+      <c r="L39" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="1">
         <v>7</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C40" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="29"/>
-      <c r="F39" s="29"/>
-      <c r="G39" s="29"/>
-      <c r="H39" s="29"/>
-      <c r="I39" s="29"/>
-      <c r="J39" s="29"/>
-      <c r="K39" s="29"/>
-      <c r="L39" s="29"/>
-      <c r="M39" s="29"/>
-      <c r="R39" s="29"/>
-    </row>
-    <row r="40" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="1">
+      <c r="D40" s="4"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="R40" s="29"/>
+    </row>
+    <row r="41" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="1">
         <v>8</v>
       </c>
-      <c r="C40" s="23" t="s">
+      <c r="C41" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="E40" s="1">
-        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="10">
-        <v>5</v>
-      </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="30">
-        <v>3</v>
-      </c>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="36">
-        <v>5</v>
-      </c>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-    </row>
-    <row r="41" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="1">
-        <v>9</v>
-      </c>
-      <c r="C41" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="D41" s="4"/>
       <c r="E41" s="1">
         <f>COUNTIF(G41:'song list'!END,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41" s="10">
-        <v>2</v>
-      </c>
-      <c r="M41" s="27">
         <v>5</v>
       </c>
-      <c r="S41" s="33">
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="29"/>
+      <c r="O41" s="30">
+        <v>3</v>
+      </c>
+      <c r="P41" s="29"/>
+      <c r="Q41" s="29"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="29"/>
+      <c r="T41" s="36">
         <v>5</v>
       </c>
+      <c r="U41" s="29"/>
+      <c r="V41" s="29"/>
+      <c r="W41" s="29"/>
     </row>
     <row r="42" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1">
-        <v>10</v>
-      </c>
-      <c r="C42" s="23" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="C42" s="31" t="s">
+        <v>6</v>
       </c>
       <c r="D42" s="4"/>
       <c r="E42" s="1">
         <f>COUNTIF(G42:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="10">
         <v>2</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="I42" s="6">
-        <v>4</v>
-      </c>
       <c r="M42" s="27">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="S42" s="33">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43" s="23" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D43" s="4"/>
       <c r="E43" s="1">
         <f>COUNTIF(G43:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="I43" s="6">
+        <v>4</v>
+      </c>
+      <c r="M43" s="27">
         <v>3</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="7">
-        <v>5</v>
-      </c>
-      <c r="L43" s="8">
-        <v>5</v>
-      </c>
-      <c r="R43" s="7">
-        <v>5</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="2"/>
+        <v>5</v>
+      </c>
+      <c r="D44" s="4"/>
       <c r="E44" s="1">
         <f>COUNTIF(G44:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G44" s="1"/>
-      <c r="K44" s="22">
-        <v>3</v>
+      <c r="H44" s="7">
+        <v>5</v>
       </c>
       <c r="L44" s="8">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="R44" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D45" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="D45" s="2"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G45" s="1"/>
-      <c r="I45" s="6">
-        <v>2</v>
-      </c>
-      <c r="N45" s="7">
-        <v>2</v>
+      <c r="K45" s="22">
+        <v>3</v>
+      </c>
+      <c r="L45" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46" s="23" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D46" s="4"/>
       <c r="E46" s="1">
         <f>COUNTIF(G46:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="7">
-        <v>1</v>
-      </c>
-      <c r="M46" s="26">
+      <c r="I46" s="6">
         <v>2</v>
       </c>
-      <c r="R46" s="7">
-        <v>1</v>
+      <c r="N46" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1">
-        <v>15</v>
-      </c>
-      <c r="C47" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D47" s="2"/>
+        <v>14</v>
+      </c>
+      <c r="C47" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="D47" s="4"/>
       <c r="E47" s="1">
         <f>COUNTIF(G47:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="7">
+        <v>1</v>
+      </c>
+      <c r="M47" s="26">
         <v>2</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="L47" s="8">
-        <v>2</v>
-      </c>
-      <c r="M47" s="28"/>
-      <c r="P47" s="27">
-        <v>5</v>
+      <c r="R47" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1">
-        <v>16</v>
-      </c>
-      <c r="C48" s="31" t="s">
-        <v>57</v>
+        <v>15</v>
+      </c>
+      <c r="C48" s="25" t="s">
+        <v>25</v>
       </c>
       <c r="D48" s="2"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F48" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G48" s="1"/>
-      <c r="K48" s="22"/>
-      <c r="L48" s="8"/>
-      <c r="U48" s="33">
+      <c r="L48" s="8">
+        <v>2</v>
+      </c>
+      <c r="M48" s="28"/>
+      <c r="P48" s="27">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" s="31" t="s">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="D49" s="2"/>
       <c r="E49" s="1">
         <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="1"/>
-      <c r="C50" s="4"/>
-      <c r="D50" s="4"/>
+      <c r="K49" s="22"/>
+      <c r="L49" s="8"/>
+      <c r="U49" s="33">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="1">
+        <v>17</v>
+      </c>
+      <c r="C50" s="31" t="s">
+        <v>24</v>
+      </c>
+      <c r="D50" s="2"/>
       <c r="E50" s="1">
         <f>COUNTIF(G50:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1815,12 +1824,10 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="38"/>
-      <c r="D51" s="19"/>
+    <row r="51" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="1"/>
+      <c r="C51" s="4"/>
+      <c r="D51" s="4"/>
       <c r="E51" s="1">
         <f>COUNTIF(G51:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1828,34 +1835,27 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="1">
-        <v>1</v>
-      </c>
-      <c r="C52" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D52" s="4"/>
+    <row r="52" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="38"/>
+      <c r="D52" s="19"/>
       <c r="E52" s="1">
         <f>COUNTIF(G52:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="1"/>
-      <c r="J52" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B53" s="1">
-        <v>2</v>
-      </c>
       <c r="C53" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D53" s="20"/>
+        <v>31</v>
+      </c>
+      <c r="D53" s="4"/>
       <c r="E53" s="1">
         <f>COUNTIF(G53:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1864,61 +1864,76 @@
         <v>2</v>
       </c>
       <c r="G53" s="1"/>
-      <c r="K53" s="22">
+      <c r="J53" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="1"/>
-      <c r="F54" s="1"/>
+    <row r="54" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="1">
+        <v>2</v>
+      </c>
+      <c r="C54" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" s="20"/>
+      <c r="E54" s="1">
+        <f>COUNTIF(G54:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K54" s="22">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2113,7 +2128,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -6688,40 +6703,46 @@
       <c r="F1017" s="1"/>
       <c r="G1017" s="1"/>
     </row>
+    <row r="1018" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1018" s="1"/>
+      <c r="F1018" s="1"/>
+      <c r="G1018" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C33:V49">
-    <sortCondition ref="C33:C49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:U31">
+    <sortCondition ref="C3:C31"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B52:C52"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C12" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
     <hyperlink ref="C27" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
-    <hyperlink ref="C29" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="C36" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="C49" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="C30" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
+    <hyperlink ref="C37" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="C50" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="C15" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="C18" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="C39" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="C40" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
     <hyperlink ref="C23" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="C4" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
     <hyperlink ref="C24" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
     <hyperlink ref="C14" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="C41" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
-    <hyperlink ref="C30" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
+    <hyperlink ref="C42" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="C31" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
     <hyperlink ref="C8" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
     <hyperlink ref="C9" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
     <hyperlink ref="C26" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
     <hyperlink ref="C16" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
     <hyperlink ref="C22" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
-    <hyperlink ref="C48" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="C49" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
     <hyperlink ref="C19" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
+    <hyperlink ref="C29" r:id="rId25" xr:uid="{32B00554-51E3-0D4A-94C8-9C35AEF9CB4F}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10909"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92E84E3A-1413-8741-AC50-5DD4CBEBFBA5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE71B5F4-FE3D-3748-AB35-F6FD45A2B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2660" yWindow="600" windowWidth="33320" windowHeight="27280" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1180" yWindow="660" windowWidth="27260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
   <si>
     <t>Key</t>
   </si>
@@ -155,9 +155,6 @@
     <t>God Bless America</t>
   </si>
   <si>
-    <t>CCLI</t>
-  </si>
-  <si>
     <t>CNT</t>
   </si>
   <si>
@@ -212,7 +209,10 @@
     <t>Turn Your Eyes Upon Jesus</t>
   </si>
   <si>
-    <t>Still</t>
+    <t>drum tab</t>
+  </si>
+  <si>
+    <t>misc</t>
   </si>
 </sst>
 </file>
@@ -367,7 +367,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -414,13 +414,6 @@
     <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="150"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -468,6 +461,12 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -688,13 +687,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1018"/>
+  <dimension ref="A1:AD1017"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
     <col min="2" max="2" width="5.5" customWidth="1"/>
     <col min="3" max="3" width="30.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.1640625" customWidth="1"/>
+    <col min="4" max="4" width="9.1640625" style="12" customWidth="1"/>
     <col min="5" max="5" width="5.5" style="5" customWidth="1"/>
     <col min="6" max="6" width="3.83203125" style="5" customWidth="1"/>
     <col min="7" max="12" width="5.5" style="5" bestFit="1" customWidth="1"/>
@@ -714,10 +713,10 @@
         <v>33</v>
       </c>
       <c r="D1" s="13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>40</v>
       </c>
       <c r="F1" s="14" t="s">
         <v>0</v>
@@ -796,12 +795,12 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="18"/>
-      <c r="E2" s="24"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="36"/>
+      <c r="E2" s="21"/>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
       <c r="H2" s="17"/>
@@ -816,25 +815,25 @@
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="D3" s="2"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="F3" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="K3" s="21">
+        <v>41</v>
+      </c>
+      <c r="K3" s="18">
         <v>1</v>
       </c>
       <c r="L3" s="1"/>
-      <c r="M3" s="26">
+      <c r="M3" s="23">
         <v>4</v>
       </c>
-      <c r="P3" s="27">
+      <c r="P3" s="24">
         <v>3</v>
       </c>
     </row>
@@ -843,10 +842,10 @@
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="31" t="s">
+      <c r="C4" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="3"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1">
         <f>COUNTIF(G4:'song list'!END,"&lt;&gt;")</f>
         <v>3</v>
@@ -856,14 +855,14 @@
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1"/>
-      <c r="Q4" s="32">
+      <c r="Q4" s="29">
         <v>2</v>
       </c>
       <c r="R4" s="1"/>
-      <c r="S4" s="33">
+      <c r="S4" s="30">
         <v>3</v>
       </c>
-      <c r="U4" s="33">
+      <c r="U4" s="30">
         <v>2</v>
       </c>
     </row>
@@ -875,7 +874,7 @@
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="3"/>
+      <c r="D5" s="1"/>
       <c r="E5" s="1">
         <f>COUNTIF(G5:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -888,10 +887,10 @@
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="2"/>
+      <c r="C6" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" s="1"/>
       <c r="E6" s="1">
         <f>COUNTIF(G6:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -901,7 +900,7 @@
       <c r="N6" s="7">
         <v>1</v>
       </c>
-      <c r="O6" s="22">
+      <c r="O6" s="19">
         <v>1</v>
       </c>
     </row>
@@ -909,10 +908,12 @@
       <c r="B7" s="1">
         <v>6</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="4"/>
+      <c r="D7" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E7" s="1">
         <f>COUNTIF(G7:'song list'!END,"&lt;&gt;")</f>
         <v>4</v>
@@ -929,7 +930,7 @@
       <c r="N7" s="7">
         <v>4</v>
       </c>
-      <c r="Q7" s="32">
+      <c r="Q7" s="29">
         <v>3</v>
       </c>
     </row>
@@ -937,10 +938,12 @@
       <c r="B8" s="1">
         <v>7</v>
       </c>
-      <c r="C8" s="31" t="s">
+      <c r="C8" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="4"/>
+      <c r="D8" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E8" s="1">
         <f>COUNTIF(G8:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -960,10 +963,10 @@
       <c r="B9" s="1">
         <v>8</v>
       </c>
-      <c r="C9" s="31" t="s">
+      <c r="C9" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D9" s="4"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="1">
         <f>COUNTIF(G9:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -974,7 +977,7 @@
       <c r="G9" s="11">
         <v>4</v>
       </c>
-      <c r="O9" s="22">
+      <c r="O9" s="19">
         <v>2</v>
       </c>
     </row>
@@ -983,9 +986,9 @@
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D10" s="2"/>
+        <v>44</v>
+      </c>
+      <c r="D10" s="1"/>
       <c r="E10" s="1">
         <f>COUNTIF(G10:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -997,10 +1000,10 @@
       <c r="B11" s="1">
         <v>10</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>43</v>
-      </c>
-      <c r="D11" s="3"/>
+      <c r="C11" s="20" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="1"/>
       <c r="E11" s="1">
         <f>COUNTIF(G11:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1009,7 +1012,7 @@
         <v>2</v>
       </c>
       <c r="G11" s="1"/>
-      <c r="M11" s="27">
+      <c r="M11" s="24">
         <v>1</v>
       </c>
     </row>
@@ -1017,32 +1020,32 @@
       <c r="B12" s="1">
         <v>11</v>
       </c>
-      <c r="C12" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="4"/>
+      <c r="C12" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="1"/>
       <c r="E12" s="1">
         <f>COUNTIF(G12:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="29"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="29"/>
-      <c r="M12" s="29"/>
-      <c r="R12" s="29"/>
+      <c r="F12" s="26"/>
+      <c r="G12" s="26"/>
+      <c r="H12" s="26"/>
+      <c r="I12" s="26"/>
+      <c r="J12" s="26"/>
+      <c r="K12" s="26"/>
+      <c r="L12" s="26"/>
+      <c r="M12" s="26"/>
+      <c r="R12" s="26"/>
     </row>
     <row r="13" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B13" s="1">
         <v>12</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="1"/>
       <c r="E13" s="1">
         <f>COUNTIF(G13:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1062,8 +1065,11 @@
       <c r="B14" s="1">
         <v>13</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="28" t="s">
         <v>9</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>57</v>
       </c>
       <c r="E14" s="1">
         <f>COUNTIF(G14:'song list'!END,"&lt;&gt;")</f>
@@ -1078,32 +1084,34 @@
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
       <c r="J14" s="5"/>
-      <c r="K14" s="22">
+      <c r="K14" s="19">
         <v>4</v>
       </c>
       <c r="L14" s="5"/>
       <c r="M14" s="5"/>
-      <c r="N14" s="29"/>
-      <c r="O14" s="29"/>
-      <c r="P14" s="29"/>
-      <c r="Q14" s="29"/>
+      <c r="N14" s="26"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="26"/>
+      <c r="Q14" s="26"/>
       <c r="R14" s="5"/>
-      <c r="S14" s="34">
+      <c r="S14" s="31">
         <v>2</v>
       </c>
-      <c r="T14" s="29"/>
-      <c r="U14" s="29"/>
-      <c r="V14" s="29"/>
-      <c r="W14" s="29"/>
+      <c r="T14" s="26"/>
+      <c r="U14" s="26"/>
+      <c r="V14" s="26"/>
+      <c r="W14" s="26"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B15" s="1">
         <v>14</v>
       </c>
-      <c r="C15" s="31" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="4"/>
+      <c r="C15" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E15" s="1">
         <f>COUNTIF(G15:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1112,10 +1120,10 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
       <c r="R15" s="1"/>
-      <c r="S15" s="33">
+      <c r="S15" s="30">
         <v>1</v>
       </c>
-      <c r="T15" s="35">
+      <c r="T15" s="32">
         <v>4</v>
       </c>
     </row>
@@ -1123,20 +1131,22 @@
       <c r="B16" s="1">
         <v>15</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="3"/>
+      <c r="D16" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E16" s="1">
         <f>COUNTIF(G16:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="P16" s="27">
+      <c r="P16" s="24">
         <v>1</v>
       </c>
-      <c r="T16" s="35">
+      <c r="T16" s="32">
         <v>3</v>
       </c>
     </row>
@@ -1144,10 +1154,12 @@
       <c r="B17" s="1">
         <v>16</v>
       </c>
-      <c r="C17" s="23" t="s">
+      <c r="C17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="4"/>
+      <c r="D17" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E17" s="1">
         <f>COUNTIF(G17:'song list'!END,"&lt;&gt;")</f>
         <v>3</v>
@@ -1168,10 +1180,10 @@
       <c r="B18" s="1">
         <v>17</v>
       </c>
-      <c r="C18" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="4"/>
+      <c r="C18" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="1"/>
       <c r="E18" s="1">
         <f>COUNTIF(G18:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1185,10 +1197,10 @@
       <c r="B19" s="1">
         <v>18</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="28" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="1">
         <f>COUNTIF(G19:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1200,7 +1212,7 @@
       <c r="L19" s="8">
         <v>1</v>
       </c>
-      <c r="U19" s="33">
+      <c r="U19" s="30">
         <v>1</v>
       </c>
     </row>
@@ -1208,10 +1220,10 @@
       <c r="B20" s="1">
         <v>19</v>
       </c>
-      <c r="C20" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="D20" s="4"/>
+      <c r="C20" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="1"/>
       <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1225,10 +1237,10 @@
       <c r="B21" s="1">
         <v>20</v>
       </c>
-      <c r="C21" s="23" t="s">
+      <c r="C21" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="4"/>
+      <c r="D21" s="1"/>
       <c r="E21" s="1">
         <f>COUNTIF(G21:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1239,7 +1251,7 @@
       <c r="G21" s="11">
         <v>1</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="30">
         <v>3</v>
       </c>
     </row>
@@ -1247,10 +1259,10 @@
       <c r="B22" s="1">
         <v>21</v>
       </c>
-      <c r="C22" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="4"/>
+      <c r="C22" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="1"/>
       <c r="E22" s="1">
         <f>COUNTIF(G22:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1264,10 +1276,12 @@
       <c r="B23" s="1">
         <v>22</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="2"/>
+      <c r="D23" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E23" s="1">
         <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1277,10 +1291,12 @@
       <c r="B24" s="1">
         <v>23</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="4"/>
+      <c r="D24" s="37" t="s">
+        <v>57</v>
+      </c>
       <c r="E24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1291,7 +1307,7 @@
       <c r="J24" s="8">
         <v>1</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="30">
         <v>4</v>
       </c>
     </row>
@@ -1299,10 +1315,10 @@
       <c r="B25" s="1">
         <v>24</v>
       </c>
-      <c r="C25" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="D25" s="4"/>
+      <c r="C25" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="1"/>
       <c r="E25" s="1">
         <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1316,10 +1332,10 @@
       <c r="B26" s="1">
         <v>25</v>
       </c>
-      <c r="C26" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="D26" s="4"/>
+      <c r="C26" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="1"/>
       <c r="E26" s="1">
         <f>COUNTIF(G26:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1333,10 +1349,10 @@
       <c r="B27" s="1">
         <v>26</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="28" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="3"/>
+      <c r="D27" s="1"/>
       <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
         <v>4</v>
@@ -1344,13 +1360,13 @@
       <c r="N27" s="7">
         <v>3</v>
       </c>
-      <c r="P27" s="27">
+      <c r="P27" s="24">
         <v>4</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="29">
         <v>1</v>
       </c>
-      <c r="T27" s="35">
+      <c r="T27" s="32">
         <v>2</v>
       </c>
     </row>
@@ -1361,7 +1377,7 @@
       <c r="C28" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D28" s="2"/>
+      <c r="D28" s="1"/>
       <c r="E28" s="1">
         <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1371,452 +1387,447 @@
       <c r="B29" s="1">
         <v>28</v>
       </c>
-      <c r="C29" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="D29" s="4"/>
+      <c r="C29" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="R29" s="1"/>
     </row>
     <row r="30" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>29</v>
       </c>
-      <c r="C30" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="D30" s="2"/>
+      <c r="C30" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="D30" s="1"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="R30" s="1"/>
+      <c r="T30" s="32">
+        <v>1</v>
+      </c>
+      <c r="U30" s="30">
+        <v>4</v>
+      </c>
     </row>
     <row r="31" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1">
-        <v>30</v>
-      </c>
-      <c r="C31" s="31" t="s">
-        <v>55</v>
-      </c>
-      <c r="D31" s="4"/>
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="1"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="T31" s="35">
-        <v>1</v>
-      </c>
-      <c r="U31" s="33">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="1"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32" s="35"/>
+      <c r="D32" s="1"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="C33" s="38"/>
-      <c r="D33" s="19"/>
+      <c r="B33" s="1">
+        <v>1</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D33" s="1"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="1"/>
+      <c r="K33" s="19">
+        <v>5</v>
+      </c>
+      <c r="O33" s="19">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="29">
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>1</v>
-      </c>
-      <c r="C34" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="D34" s="2"/>
+        <v>2</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D34" s="1"/>
       <c r="E34" s="1">
         <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F34" s="1"/>
       <c r="G34" s="1"/>
-      <c r="K34" s="22">
-        <v>5</v>
-      </c>
-      <c r="O34" s="22">
-        <v>5</v>
-      </c>
-      <c r="Q34" s="32">
-        <v>5</v>
-      </c>
     </row>
     <row r="35" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
-        <v>2</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D35" s="2"/>
+        <v>3</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="D35" s="1"/>
       <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
+      <c r="I35" s="6">
+        <v>5</v>
+      </c>
+      <c r="P35" s="24">
+        <v>2</v>
+      </c>
     </row>
     <row r="36" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
-        <v>3</v>
-      </c>
-      <c r="C36" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="D36" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="C36" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36" s="1"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="I36" s="6">
+      <c r="N36" s="7">
         <v>5</v>
-      </c>
-      <c r="P36" s="27">
-        <v>2</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
-        <v>4</v>
-      </c>
-      <c r="C37" s="31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D37" s="4"/>
+        <v>5</v>
+      </c>
+      <c r="C37" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="D37" s="1"/>
       <c r="E37" s="1">
         <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F37" s="1"/>
+      <c r="F37" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="G37" s="1"/>
-      <c r="N37" s="7">
-        <v>5</v>
+      <c r="J37" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="38" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
-        <v>5</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>12</v>
-      </c>
-      <c r="D38" s="4"/>
+        <v>6</v>
+      </c>
+      <c r="C38" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D38" s="1"/>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="G38" s="1"/>
       <c r="J38" s="8">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="L38" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q38" s="29">
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
+        <v>7</v>
+      </c>
+      <c r="C39" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="26"/>
+      <c r="F39" s="26"/>
+      <c r="G39" s="26"/>
+      <c r="H39" s="26"/>
+      <c r="I39" s="26"/>
+      <c r="J39" s="26"/>
+      <c r="K39" s="26"/>
+      <c r="L39" s="26"/>
+      <c r="M39" s="26"/>
+      <c r="R39" s="26"/>
+    </row>
+    <row r="40" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="1">
+        <v>8</v>
+      </c>
+      <c r="C40" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D40" s="1"/>
+      <c r="E40" s="1">
+        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G40" s="10">
+        <v>5</v>
+      </c>
+      <c r="H40" s="5"/>
+      <c r="I40" s="5"/>
+      <c r="J40" s="5"/>
+      <c r="K40" s="5"/>
+      <c r="L40" s="5"/>
+      <c r="M40" s="5"/>
+      <c r="N40" s="26"/>
+      <c r="O40" s="27">
+        <v>3</v>
+      </c>
+      <c r="P40" s="26"/>
+      <c r="Q40" s="26"/>
+      <c r="R40" s="5"/>
+      <c r="S40" s="26"/>
+      <c r="T40" s="33">
+        <v>5</v>
+      </c>
+      <c r="U40" s="26"/>
+      <c r="V40" s="26"/>
+      <c r="W40" s="26"/>
+    </row>
+    <row r="41" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="1">
+        <v>9</v>
+      </c>
+      <c r="C41" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="C39" s="23" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="4"/>
-      <c r="E39" s="1">
-        <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F39" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G39" s="1"/>
-      <c r="J39" s="8">
-        <v>5</v>
-      </c>
-      <c r="L39" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q39" s="32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="1">
-        <v>7</v>
-      </c>
-      <c r="C40" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="D40" s="4"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="R40" s="29"/>
-    </row>
-    <row r="41" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="1">
-        <v>8</v>
-      </c>
-      <c r="C41" s="23" t="s">
-        <v>22</v>
-      </c>
+      <c r="D41" s="1"/>
       <c r="E41" s="1">
         <f>COUNTIF(G41:'song list'!END,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G41" s="10">
         <v>2</v>
       </c>
-      <c r="G41" s="10">
+      <c r="M41" s="24">
         <v>5</v>
       </c>
-      <c r="H41" s="5"/>
-      <c r="I41" s="5"/>
-      <c r="J41" s="5"/>
-      <c r="K41" s="5"/>
-      <c r="L41" s="5"/>
-      <c r="M41" s="5"/>
-      <c r="N41" s="29"/>
-      <c r="O41" s="30">
-        <v>3</v>
-      </c>
-      <c r="P41" s="29"/>
-      <c r="Q41" s="29"/>
-      <c r="R41" s="5"/>
-      <c r="S41" s="29"/>
-      <c r="T41" s="36">
+      <c r="S41" s="30">
         <v>5</v>
       </c>
-      <c r="U41" s="29"/>
-      <c r="V41" s="29"/>
-      <c r="W41" s="29"/>
     </row>
     <row r="42" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1">
-        <v>9</v>
-      </c>
-      <c r="C42" s="31" t="s">
-        <v>6</v>
-      </c>
-      <c r="D42" s="4"/>
+        <v>10</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D42" s="1"/>
       <c r="E42" s="1">
         <f>COUNTIF(G42:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F42" s="1"/>
+      <c r="G42" s="1"/>
+      <c r="I42" s="6">
+        <v>4</v>
+      </c>
+      <c r="M42" s="24">
         <v>3</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G42" s="10">
-        <v>2</v>
-      </c>
-      <c r="M42" s="27">
-        <v>5</v>
-      </c>
-      <c r="S42" s="33">
-        <v>5</v>
       </c>
     </row>
     <row r="43" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1">
-        <v>10</v>
-      </c>
-      <c r="C43" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="D43" s="4"/>
+        <v>11</v>
+      </c>
+      <c r="C43" s="20" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="1"/>
       <c r="E43" s="1">
         <f>COUNTIF(G43:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F43" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F43" s="1"/>
       <c r="G43" s="1"/>
-      <c r="I43" s="6">
-        <v>4</v>
-      </c>
-      <c r="M43" s="27">
-        <v>3</v>
+      <c r="H43" s="7">
+        <v>5</v>
+      </c>
+      <c r="L43" s="8">
+        <v>5</v>
+      </c>
+      <c r="R43" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1">
-        <v>11</v>
-      </c>
-      <c r="C44" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="D44" s="4"/>
+        <v>12</v>
+      </c>
+      <c r="C44" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" s="1"/>
       <c r="E44" s="1">
         <f>COUNTIF(G44:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G44" s="1"/>
-      <c r="H44" s="7">
-        <v>5</v>
+      <c r="K44" s="19">
+        <v>3</v>
       </c>
       <c r="L44" s="8">
-        <v>5</v>
-      </c>
-      <c r="R44" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1">
-        <v>12</v>
-      </c>
-      <c r="C45" s="23" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="C45" s="20" t="s">
+        <v>19</v>
+      </c>
+      <c r="D45" s="1"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="1"/>
+      <c r="G45" s="1"/>
+      <c r="I45" s="6">
         <v>2</v>
       </c>
-      <c r="G45" s="1"/>
-      <c r="K45" s="22">
-        <v>3</v>
-      </c>
-      <c r="L45" s="8">
-        <v>3</v>
+      <c r="N45" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1">
-        <v>13</v>
-      </c>
-      <c r="C46" s="23" t="s">
-        <v>19</v>
-      </c>
-      <c r="D46" s="4"/>
+        <v>14</v>
+      </c>
+      <c r="C46" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D46" s="1"/>
       <c r="E46" s="1">
         <f>COUNTIF(G46:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="I46" s="6">
+      <c r="H46" s="7">
+        <v>1</v>
+      </c>
+      <c r="M46" s="23">
         <v>2</v>
       </c>
-      <c r="N46" s="7">
-        <v>2</v>
+      <c r="R46" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1">
-        <v>14</v>
-      </c>
-      <c r="C47" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="D47" s="4"/>
+        <v>15</v>
+      </c>
+      <c r="C47" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="D47" s="1"/>
       <c r="E47" s="1">
         <f>COUNTIF(G47:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F47" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F47" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G47" s="1"/>
-      <c r="H47" s="7">
-        <v>1</v>
-      </c>
-      <c r="M47" s="26">
+      <c r="L47" s="8">
         <v>2</v>
       </c>
-      <c r="R47" s="7">
-        <v>1</v>
+      <c r="M47" s="25"/>
+      <c r="P47" s="24">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1">
-        <v>15</v>
-      </c>
-      <c r="C48" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="D48" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="C48" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="D48" s="1"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F48" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="F48" s="1"/>
       <c r="G48" s="1"/>
-      <c r="L48" s="8">
-        <v>2</v>
-      </c>
-      <c r="M48" s="28"/>
-      <c r="P48" s="27">
+      <c r="K48" s="19"/>
+      <c r="L48" s="8"/>
+      <c r="U48" s="30">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1">
-        <v>16</v>
-      </c>
-      <c r="C49" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="D49" s="2"/>
+        <v>17</v>
+      </c>
+      <c r="C49" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="D49" s="1"/>
       <c r="E49" s="1">
         <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-      <c r="K49" s="22"/>
-      <c r="L49" s="8"/>
-      <c r="U49" s="33">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="1">
-        <v>17</v>
-      </c>
-      <c r="C50" s="31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D50" s="2"/>
+    </row>
+    <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="1"/>
+      <c r="C50" s="4"/>
+      <c r="D50" s="1"/>
       <c r="E50" s="1">
         <f>COUNTIF(G50:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1824,10 +1835,12 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="1"/>
-      <c r="C51" s="4"/>
-      <c r="D51" s="4"/>
+    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="35"/>
+      <c r="D51" s="1"/>
       <c r="E51" s="1">
         <f>COUNTIF(G51:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
@@ -1835,27 +1848,33 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="19"/>
+    <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="1">
+        <v>1</v>
+      </c>
+      <c r="C52" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" s="1"/>
       <c r="E52" s="1">
         <f>COUNTIF(G52:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F52" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="F52" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G52" s="1"/>
-    </row>
-    <row r="53" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J52" s="8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1">
-        <v>1</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>31</v>
-      </c>
-      <c r="D53" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="C53" s="20" t="s">
+        <v>38</v>
+      </c>
       <c r="E53" s="1">
         <f>COUNTIF(G53:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1864,76 +1883,61 @@
         <v>2</v>
       </c>
       <c r="G53" s="1"/>
-      <c r="J53" s="8">
+      <c r="K53" s="19">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="1">
-        <v>2</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>38</v>
-      </c>
-      <c r="D54" s="20"/>
-      <c r="E54" s="1">
-        <f>COUNTIF(G54:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F54" s="1" t="s">
-        <v>2</v>
-      </c>
+    <row r="54" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="1"/>
+      <c r="F54" s="1"/>
       <c r="G54" s="1"/>
-      <c r="K54" s="22">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="55" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2128,7 +2132,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:7" ht="13" x14ac:dyDescent="0.15">
       <c r="B103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -6703,46 +6707,48 @@
       <c r="F1017" s="1"/>
       <c r="G1017" s="1"/>
     </row>
-    <row r="1018" spans="2:7" ht="13" x14ac:dyDescent="0.15">
-      <c r="B1018" s="1"/>
-      <c r="F1018" s="1"/>
-      <c r="G1018" s="1"/>
-    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C3:U31">
-    <sortCondition ref="C3:C31"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C33:V49">
+    <sortCondition ref="C33:C49"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="B52:C52"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="B51:C51"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C12" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
     <hyperlink ref="C27" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
-    <hyperlink ref="C30" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="C37" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="C50" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="C29" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
+    <hyperlink ref="C36" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="C49" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="C15" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="C18" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="C40" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="C39" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
     <hyperlink ref="C23" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="C4" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
     <hyperlink ref="C24" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
     <hyperlink ref="C14" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="C42" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
-    <hyperlink ref="C31" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
+    <hyperlink ref="C41" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="C30" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
     <hyperlink ref="C8" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
     <hyperlink ref="C9" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
     <hyperlink ref="C26" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
     <hyperlink ref="C16" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
     <hyperlink ref="C22" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
-    <hyperlink ref="C49" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="C48" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
     <hyperlink ref="C19" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
-    <hyperlink ref="C29" r:id="rId25" xr:uid="{32B00554-51E3-0D4A-94C8-9C35AEF9CB4F}"/>
+    <hyperlink ref="D8" r:id="rId25" xr:uid="{93134F2E-198C-D74C-8193-8EFB343FFEA8}"/>
+    <hyperlink ref="D24" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
+    <hyperlink ref="D17" r:id="rId27" xr:uid="{2B2EFF17-7C8B-7E47-99BF-2437146F3F4A}"/>
+    <hyperlink ref="D14" r:id="rId28" xr:uid="{8FEF4FFD-A276-7946-98B4-C48564B7D962}"/>
+    <hyperlink ref="D7" r:id="rId29" xr:uid="{7F154C3C-C716-3646-BC29-496637A29377}"/>
+    <hyperlink ref="D23" r:id="rId30" xr:uid="{72810517-3CD0-5643-BFD6-2E9EE7C0EF4B}"/>
+    <hyperlink ref="D16" r:id="rId31" xr:uid="{259F3BD9-4FE0-074B-BD50-3B5872B6B78E}"/>
+    <hyperlink ref="D15" r:id="rId32" xr:uid="{FA8C1C39-EFA7-F046-815E-CD6C35742B9B}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10914"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE71B5F4-FE3D-3748-AB35-F6FD45A2B70B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DE8E71-5B0C-B541-8512-8EADEED905DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1180" yWindow="660" windowWidth="27260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1720" yWindow="660" windowWidth="27260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
   <si>
     <t>Key</t>
   </si>
@@ -214,6 +214,9 @@
   <si>
     <t>misc</t>
   </si>
+  <si>
+    <t>In Jesus Name (God of Possible)</t>
+  </si>
 </sst>
 </file>
 
@@ -367,7 +370,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -456,16 +459,19 @@
     <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -687,7 +693,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:AD1017"/>
+  <dimension ref="A1:AD1018"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="3.5" customWidth="1"/>
@@ -795,11 +801,11 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="36"/>
+      <c r="C2" s="37"/>
+      <c r="D2" s="34"/>
       <c r="E2" s="21"/>
       <c r="F2" s="16"/>
       <c r="G2" s="17"/>
@@ -821,7 +827,7 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1">
         <f>COUNTIF(G3:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F3" s="12" t="s">
         <v>41</v>
@@ -835,6 +841,9 @@
       </c>
       <c r="P3" s="24">
         <v>3</v>
+      </c>
+      <c r="V3" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -911,7 +920,7 @@
       <c r="C7" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E7" s="1">
@@ -941,12 +950,12 @@
       <c r="C8" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="D8" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E8" s="1">
         <f>COUNTIF(G8:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>4</v>
@@ -957,6 +966,9 @@
       </c>
       <c r="R8" s="7">
         <v>2</v>
+      </c>
+      <c r="V8" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1068,12 +1080,12 @@
       <c r="C14" s="28" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="37" t="s">
+      <c r="D14" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E14" s="1">
         <f>COUNTIF(G14:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F14" s="1" t="s">
         <v>4</v>
@@ -1099,7 +1111,9 @@
       </c>
       <c r="T14" s="26"/>
       <c r="U14" s="26"/>
-      <c r="V14" s="26"/>
+      <c r="V14" s="38">
+        <v>4</v>
+      </c>
       <c r="W14" s="26"/>
     </row>
     <row r="15" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1109,7 +1123,7 @@
       <c r="C15" s="28" t="s">
         <v>48</v>
       </c>
-      <c r="D15" s="37" t="s">
+      <c r="D15" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E15" s="1">
@@ -1134,7 +1148,7 @@
       <c r="C16" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="D16" s="37" t="s">
+      <c r="D16" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E16" s="1">
@@ -1150,14 +1164,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
       <c r="C17" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="D17" s="37" t="s">
+      <c r="D17" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E17" s="1">
@@ -1176,7 +1190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1193,7 +1207,7 @@
       <c r="H18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1216,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1226,14 +1240,17 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="R20" s="1"/>
-    </row>
-    <row r="21" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V20" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1255,7 +1272,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1272,68 +1289,71 @@
       <c r="H22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
       <c r="C23" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>57</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="D23" s="1"/>
       <c r="E23" s="1">
         <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>1</v>
+      </c>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="R23" s="1"/>
+      <c r="V23" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
       <c r="C24" s="28" t="s">
-        <v>14</v>
-      </c>
-      <c r="D24" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="D24" s="35" t="s">
         <v>57</v>
       </c>
       <c r="E24" s="1">
         <f>COUNTIF(G24:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="J24" s="8">
-        <v>1</v>
-      </c>
-      <c r="S24" s="30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
       <c r="C25" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="D25" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="D25" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="E25" s="1">
         <f>COUNTIF(G25:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="J25" s="8">
+        <v>1</v>
+      </c>
+      <c r="S25" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
       <c r="C26" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1">
@@ -1345,96 +1365,102 @@
       <c r="H26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
       <c r="C27" s="28" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1">
         <f>COUNTIF(G27:'song list'!END,"&lt;&gt;")</f>
-        <v>4</v>
-      </c>
-      <c r="N27" s="7">
-        <v>3</v>
-      </c>
-      <c r="P27" s="24">
-        <v>4</v>
-      </c>
-      <c r="Q27" s="29">
-        <v>1</v>
-      </c>
-      <c r="T27" s="32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="R27" s="1"/>
+    </row>
+    <row r="28" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>26</v>
+      <c r="C28" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1">
         <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+      <c r="N28" s="7">
+        <v>3</v>
+      </c>
+      <c r="P28" s="24">
+        <v>4</v>
+      </c>
+      <c r="Q28" s="29">
+        <v>1</v>
+      </c>
+      <c r="T28" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>28</v>
       </c>
-      <c r="C29" s="28" t="s">
-        <v>45</v>
+      <c r="C29" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1">
         <f>COUNTIF(G29:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-    </row>
-    <row r="30" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="30" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>29</v>
       </c>
       <c r="C30" s="28" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1">
         <f>COUNTIF(G30:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="T30" s="32">
-        <v>1</v>
-      </c>
-      <c r="U30" s="30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="31" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B31" s="1"/>
-      <c r="C31" s="2"/>
+    </row>
+    <row r="31" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B31" s="1">
+        <v>30</v>
+      </c>
+      <c r="C31" s="28" t="s">
+        <v>54</v>
+      </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B32" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C32" s="35"/>
+        <v>2</v>
+      </c>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="R31" s="1"/>
+      <c r="T31" s="32">
+        <v>1</v>
+      </c>
+      <c r="U31" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1">
         <f>COUNTIF(G32:'song list'!END,"&lt;&gt;")</f>
@@ -1442,195 +1468,167 @@
       </c>
     </row>
     <row r="33" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="1">
-        <v>1</v>
-      </c>
-      <c r="C33" s="20" t="s">
-        <v>32</v>
-      </c>
+      <c r="B33" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="C33" s="37"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="1"/>
-      <c r="K33" s="19">
-        <v>5</v>
-      </c>
-      <c r="O33" s="19">
-        <v>5</v>
-      </c>
-      <c r="Q33" s="29">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B34" s="1">
-        <v>2</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1">
         <f>COUNTIF(G34:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="F34" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G34" s="1"/>
+      <c r="K34" s="19">
+        <v>5</v>
+      </c>
+      <c r="O34" s="19">
+        <v>5</v>
+      </c>
+      <c r="Q34" s="29">
+        <v>5</v>
+      </c>
     </row>
     <row r="35" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B35" s="1">
-        <v>3</v>
-      </c>
-      <c r="C35" s="20" t="s">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1">
         <f>COUNTIF(G35:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
-      <c r="I35" s="6">
-        <v>5</v>
-      </c>
-      <c r="P35" s="24">
-        <v>2</v>
-      </c>
     </row>
     <row r="36" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B36" s="1">
-        <v>4</v>
-      </c>
-      <c r="C36" s="28" t="s">
-        <v>47</v>
+        <v>3</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
         <f>COUNTIF(G36:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
-      <c r="N36" s="7">
+      <c r="I36" s="6">
         <v>5</v>
+      </c>
+      <c r="P36" s="24">
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B37" s="1">
-        <v>5</v>
-      </c>
-      <c r="C37" s="20" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="C37" s="28" t="s">
+        <v>47</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
         <f>COUNTIF(G37:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="F37" s="1"/>
       <c r="G37" s="1"/>
-      <c r="J37" s="8">
-        <v>3</v>
+      <c r="N37" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B38" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C38" s="20" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
         <f>COUNTIF(G38:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="G38" s="1"/>
       <c r="J38" s="8">
-        <v>5</v>
-      </c>
-      <c r="L38" s="8">
-        <v>4</v>
-      </c>
-      <c r="Q38" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B39" s="1">
+        <v>6</v>
+      </c>
+      <c r="C39" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="D39" s="1"/>
+      <c r="E39" s="1">
+        <f>COUNTIF(G39:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F39" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="1"/>
+      <c r="J39" s="8">
+        <v>5</v>
+      </c>
+      <c r="L39" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q39" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B40" s="1">
         <v>7</v>
       </c>
-      <c r="C39" s="28" t="s">
+      <c r="C40" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="D39" s="1"/>
-      <c r="E39" s="26"/>
-      <c r="F39" s="26"/>
-      <c r="G39" s="26"/>
-      <c r="H39" s="26"/>
-      <c r="I39" s="26"/>
-      <c r="J39" s="26"/>
-      <c r="K39" s="26"/>
-      <c r="L39" s="26"/>
-      <c r="M39" s="26"/>
-      <c r="R39" s="26"/>
-    </row>
-    <row r="40" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B40" s="1">
+      <c r="D40" s="1"/>
+      <c r="E40" s="26"/>
+      <c r="F40" s="26"/>
+      <c r="G40" s="26"/>
+      <c r="H40" s="26"/>
+      <c r="I40" s="26"/>
+      <c r="J40" s="26"/>
+      <c r="K40" s="26"/>
+      <c r="L40" s="26"/>
+      <c r="M40" s="26"/>
+      <c r="R40" s="26"/>
+    </row>
+    <row r="41" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B41" s="1">
         <v>8</v>
       </c>
-      <c r="C40" s="20" t="s">
+      <c r="C41" s="20" t="s">
         <v>22</v>
-      </c>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1">
-        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="F40" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="10">
-        <v>5</v>
-      </c>
-      <c r="H40" s="5"/>
-      <c r="I40" s="5"/>
-      <c r="J40" s="5"/>
-      <c r="K40" s="5"/>
-      <c r="L40" s="5"/>
-      <c r="M40" s="5"/>
-      <c r="N40" s="26"/>
-      <c r="O40" s="27">
-        <v>3</v>
-      </c>
-      <c r="P40" s="26"/>
-      <c r="Q40" s="26"/>
-      <c r="R40" s="5"/>
-      <c r="S40" s="26"/>
-      <c r="T40" s="33">
-        <v>5</v>
-      </c>
-      <c r="U40" s="26"/>
-      <c r="V40" s="26"/>
-      <c r="W40" s="26"/>
-    </row>
-    <row r="41" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B41" s="1">
-        <v>9</v>
-      </c>
-      <c r="C41" s="28" t="s">
-        <v>6</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1">
@@ -1638,195 +1636,223 @@
         <v>3</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G41" s="10">
-        <v>2</v>
-      </c>
-      <c r="M41" s="24">
         <v>5</v>
       </c>
-      <c r="S41" s="30">
+      <c r="H41" s="5"/>
+      <c r="I41" s="5"/>
+      <c r="J41" s="5"/>
+      <c r="K41" s="5"/>
+      <c r="L41" s="5"/>
+      <c r="M41" s="5"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="27">
+        <v>3</v>
+      </c>
+      <c r="P41" s="26"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="5"/>
+      <c r="S41" s="26"/>
+      <c r="T41" s="33">
         <v>5</v>
       </c>
+      <c r="U41" s="26"/>
+      <c r="V41" s="26"/>
+      <c r="W41" s="26"/>
     </row>
     <row r="42" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B42" s="1">
-        <v>10</v>
-      </c>
-      <c r="C42" s="20" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="C42" s="28" t="s">
+        <v>6</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1">
         <f>COUNTIF(G42:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G42" s="10">
         <v>2</v>
       </c>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="I42" s="6">
-        <v>4</v>
-      </c>
       <c r="M42" s="24">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="S42" s="30">
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B43" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C43" s="20" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1">
         <f>COUNTIF(G43:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="G43" s="1"/>
+      <c r="I43" s="6">
+        <v>4</v>
+      </c>
+      <c r="M43" s="24">
         <v>3</v>
-      </c>
-      <c r="F43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="7">
-        <v>5</v>
-      </c>
-      <c r="L43" s="8">
-        <v>5</v>
-      </c>
-      <c r="R43" s="7">
-        <v>5</v>
       </c>
     </row>
     <row r="44" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B44" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C44" s="20" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1">
         <f>COUNTIF(G44:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F44" s="1" t="s">
         <v>2</v>
       </c>
       <c r="G44" s="1"/>
-      <c r="K44" s="19">
-        <v>3</v>
+      <c r="H44" s="7">
+        <v>5</v>
       </c>
       <c r="L44" s="8">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="R44" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="45" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B45" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C45" s="20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1">
         <f>COUNTIF(G45:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="F45" s="1"/>
+      <c r="F45" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G45" s="1"/>
-      <c r="I45" s="6">
-        <v>2</v>
-      </c>
-      <c r="N45" s="7">
-        <v>2</v>
+      <c r="K45" s="19">
+        <v>3</v>
+      </c>
+      <c r="L45" s="8">
+        <v>3</v>
       </c>
     </row>
     <row r="46" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B46" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1">
         <f>COUNTIF(G46:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
-      <c r="H46" s="7">
-        <v>1</v>
-      </c>
-      <c r="M46" s="23">
+      <c r="I46" s="6">
         <v>2</v>
       </c>
-      <c r="R46" s="7">
-        <v>1</v>
+      <c r="N46" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B47" s="1">
-        <v>15</v>
-      </c>
-      <c r="C47" s="22" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="C47" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1">
         <f>COUNTIF(G47:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="F47" s="1"/>
+      <c r="G47" s="1"/>
+      <c r="H47" s="7">
+        <v>1</v>
+      </c>
+      <c r="M47" s="23">
         <v>2</v>
       </c>
-      <c r="F47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="1"/>
-      <c r="L47" s="8">
-        <v>2</v>
-      </c>
-      <c r="M47" s="25"/>
-      <c r="P47" s="24">
-        <v>5</v>
+      <c r="R47" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B48" s="1">
-        <v>16</v>
-      </c>
-      <c r="C48" s="28" t="s">
-        <v>56</v>
+        <v>15</v>
+      </c>
+      <c r="C48" s="22" t="s">
+        <v>25</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1">
         <f>COUNTIF(G48:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="F48" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="F48" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G48" s="1"/>
-      <c r="K48" s="19"/>
-      <c r="L48" s="8"/>
-      <c r="U48" s="30">
+      <c r="L48" s="8">
+        <v>2</v>
+      </c>
+      <c r="M48" s="25"/>
+      <c r="P48" s="24">
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C49" s="28" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1">
         <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
-    </row>
-    <row r="50" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B50" s="1"/>
-      <c r="C50" s="4"/>
+      <c r="K49" s="19"/>
+      <c r="L49" s="8"/>
+      <c r="U49" s="30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B50" s="1">
+        <v>17</v>
+      </c>
+      <c r="C50" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1">
         <f>COUNTIF(G50:'song list'!END,"&lt;&gt;")</f>
@@ -1835,11 +1861,9 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B51" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C51" s="35"/>
+    <row r="51" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B51" s="1"/>
+      <c r="C51" s="4"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1">
         <f>COUNTIF(G51:'song list'!END,"&lt;&gt;")</f>
@@ -1848,33 +1872,27 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="1">
-        <v>1</v>
-      </c>
-      <c r="C52" s="20" t="s">
-        <v>31</v>
-      </c>
+    <row r="52" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="37"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1">
         <f>COUNTIF(G52:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+    </row>
+    <row r="53" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B53" s="1">
         <v>1</v>
       </c>
-      <c r="F52" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="1"/>
-      <c r="J52" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="53" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B53" s="1">
-        <v>2</v>
-      </c>
       <c r="C53" s="20" t="s">
-        <v>38</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="D53" s="1"/>
       <c r="E53" s="1">
         <f>COUNTIF(G53:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1883,61 +1901,75 @@
         <v>2</v>
       </c>
       <c r="G53" s="1"/>
-      <c r="K53" s="19">
+      <c r="J53" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B54" s="1"/>
-      <c r="F54" s="1"/>
+    <row r="54" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B54" s="1">
+        <v>2</v>
+      </c>
+      <c r="C54" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E54" s="1">
+        <f>COUNTIF(G54:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="F54" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="G54" s="1"/>
-    </row>
-    <row r="55" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K54" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -2132,7 +2164,7 @@
       <c r="F102" s="1"/>
       <c r="G102" s="1"/>
     </row>
-    <row r="103" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+    <row r="103" spans="2:7" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B103" s="1"/>
       <c r="F103" s="1"/>
       <c r="G103" s="1"/>
@@ -6707,46 +6739,51 @@
       <c r="F1017" s="1"/>
       <c r="G1017" s="1"/>
     </row>
+    <row r="1018" spans="2:7" ht="13" x14ac:dyDescent="0.15">
+      <c r="B1018" s="1"/>
+      <c r="F1018" s="1"/>
+      <c r="G1018" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C33:V49">
-    <sortCondition ref="C33:C49"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="C34:V50">
+    <sortCondition ref="C34:C50"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="B51:C51"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="B52:C52"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C12" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
-    <hyperlink ref="C27" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
-    <hyperlink ref="C29" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="C36" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="C49" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="C28" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
+    <hyperlink ref="C30" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
+    <hyperlink ref="C37" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="C50" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="C15" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="C18" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="C20" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="C39" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
-    <hyperlink ref="C25" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
+    <hyperlink ref="C40" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="C26" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="C6" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
-    <hyperlink ref="C23" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
+    <hyperlink ref="C24" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="C4" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
-    <hyperlink ref="C24" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
+    <hyperlink ref="C25" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
     <hyperlink ref="C14" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="C41" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
-    <hyperlink ref="C30" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
+    <hyperlink ref="C42" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="C31" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
     <hyperlink ref="C8" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
     <hyperlink ref="C9" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
-    <hyperlink ref="C26" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
+    <hyperlink ref="C27" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
     <hyperlink ref="C16" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
     <hyperlink ref="C22" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
-    <hyperlink ref="C48" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="C49" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
     <hyperlink ref="C19" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
     <hyperlink ref="D8" r:id="rId25" xr:uid="{93134F2E-198C-D74C-8193-8EFB343FFEA8}"/>
-    <hyperlink ref="D24" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
+    <hyperlink ref="D25" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
     <hyperlink ref="D17" r:id="rId27" xr:uid="{2B2EFF17-7C8B-7E47-99BF-2437146F3F4A}"/>
     <hyperlink ref="D14" r:id="rId28" xr:uid="{8FEF4FFD-A276-7946-98B4-C48564B7D962}"/>
     <hyperlink ref="D7" r:id="rId29" xr:uid="{7F154C3C-C716-3646-BC29-496637A29377}"/>
-    <hyperlink ref="D23" r:id="rId30" xr:uid="{72810517-3CD0-5643-BFD6-2E9EE7C0EF4B}"/>
+    <hyperlink ref="D24" r:id="rId30" xr:uid="{72810517-3CD0-5643-BFD6-2E9EE7C0EF4B}"/>
     <hyperlink ref="D16" r:id="rId31" xr:uid="{259F3BD9-4FE0-074B-BD50-3B5872B6B78E}"/>
     <hyperlink ref="D15" r:id="rId32" xr:uid="{FA8C1C39-EFA7-F046-815E-CD6C35742B9B}"/>
   </hyperlinks>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8DE8E71-5B0C-B541-8512-8EADEED905DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61414C1B-F12A-2141-85AD-B466E11FD659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1720" yWindow="660" windowWidth="27260" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29220" yWindow="-3980" windowWidth="28540" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
   <si>
     <t>Key</t>
   </si>
@@ -465,14 +465,14 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -801,10 +801,10 @@
       </c>
     </row>
     <row r="2" spans="1:30" ht="13" x14ac:dyDescent="0.15">
-      <c r="B2" s="36" t="s">
+      <c r="B2" s="37" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="37"/>
+      <c r="C2" s="38"/>
       <c r="D2" s="34"/>
       <c r="E2" s="21"/>
       <c r="F2" s="16"/>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="T14" s="26"/>
       <c r="U14" s="26"/>
-      <c r="V14" s="38">
+      <c r="V14" s="36">
         <v>4</v>
       </c>
       <c r="W14" s="26"/>
@@ -1164,7 +1164,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B17" s="1">
         <v>16</v>
       </c>
@@ -1190,7 +1190,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="1">
         <v>17</v>
       </c>
@@ -1207,7 +1207,7 @@
       <c r="H18" s="1"/>
       <c r="R18" s="1"/>
     </row>
-    <row r="19" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B19" s="1">
         <v>18</v>
       </c>
@@ -1230,7 +1230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B20" s="1">
         <v>19</v>
       </c>
@@ -1240,7 +1240,7 @@
       <c r="D20" s="1"/>
       <c r="E20" s="1">
         <f>COUNTIF(G20:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1249,8 +1249,11 @@
       <c r="V20" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="21" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W20" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B21" s="1">
         <v>20</v>
       </c>
@@ -1272,7 +1275,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="1">
         <v>21</v>
       </c>
@@ -1289,7 +1292,7 @@
       <c r="H22" s="1"/>
       <c r="R22" s="1"/>
     </row>
-    <row r="23" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B23" s="1">
         <v>22</v>
       </c>
@@ -1299,7 +1302,7 @@
       <c r="D23" s="1"/>
       <c r="E23" s="1">
         <f>COUNTIF(G23:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
@@ -1308,8 +1311,11 @@
       <c r="V23" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="24" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W23" s="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B24" s="1">
         <v>23</v>
       </c>
@@ -1324,7 +1330,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B25" s="1">
         <v>24</v>
       </c>
@@ -1348,7 +1354,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B26" s="1">
         <v>25</v>
       </c>
@@ -1365,7 +1371,7 @@
       <c r="H26" s="1"/>
       <c r="R26" s="1"/>
     </row>
-    <row r="27" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B27" s="1">
         <v>26</v>
       </c>
@@ -1382,7 +1388,7 @@
       <c r="H27" s="1"/>
       <c r="R27" s="1"/>
     </row>
-    <row r="28" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B28" s="1">
         <v>27</v>
       </c>
@@ -1392,7 +1398,7 @@
       <c r="D28" s="1"/>
       <c r="E28" s="1">
         <f>COUNTIF(G28:'song list'!END,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N28" s="7">
         <v>3</v>
@@ -1406,8 +1412,11 @@
       <c r="T28" s="32">
         <v>2</v>
       </c>
-    </row>
-    <row r="29" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W28" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B29" s="1">
         <v>28</v>
       </c>
@@ -1420,7 +1429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B30" s="1">
         <v>29</v>
       </c>
@@ -1435,14 +1444,16 @@
       <c r="F30" s="1"/>
       <c r="G30" s="1"/>
     </row>
-    <row r="31" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B31" s="1">
         <v>30</v>
       </c>
       <c r="C31" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="D31" s="1"/>
+      <c r="D31" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="E31" s="1">
         <f>COUNTIF(G31:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
@@ -1458,7 +1469,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="2:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B32" s="1"/>
       <c r="C32" s="2"/>
       <c r="D32" s="1"/>
@@ -1468,10 +1479,10 @@
       </c>
     </row>
     <row r="33" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B33" s="36" t="s">
+      <c r="B33" s="37" t="s">
         <v>35</v>
       </c>
-      <c r="C33" s="37"/>
+      <c r="C33" s="38"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1">
         <f>COUNTIF(G33:'song list'!END,"&lt;&gt;")</f>
@@ -1612,7 +1623,10 @@
         <v>51</v>
       </c>
       <c r="D40" s="1"/>
-      <c r="E40" s="26"/>
+      <c r="E40" s="1">
+        <f>COUNTIF(G40:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
       <c r="F40" s="26"/>
       <c r="G40" s="26"/>
       <c r="H40" s="26"/>
@@ -1622,6 +1636,9 @@
       <c r="L40" s="26"/>
       <c r="M40" s="26"/>
       <c r="R40" s="26"/>
+      <c r="W40" s="32">
+        <v>1</v>
+      </c>
     </row>
     <row r="41" spans="2:23" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B41" s="1">
@@ -1826,7 +1843,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B49" s="1">
         <v>16</v>
       </c>
@@ -1836,7 +1853,7 @@
       <c r="D49" s="1"/>
       <c r="E49" s="1">
         <f>COUNTIF(G49:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F49" s="1"/>
       <c r="G49" s="1"/>
@@ -1845,8 +1862,11 @@
       <c r="U49" s="30">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="W49" s="32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="50" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B50" s="1">
         <v>17</v>
       </c>
@@ -1861,7 +1881,7 @@
       <c r="F50" s="1"/>
       <c r="G50" s="1"/>
     </row>
-    <row r="51" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B51" s="1"/>
       <c r="C51" s="4"/>
       <c r="D51" s="1"/>
@@ -1872,11 +1892,11 @@
       <c r="F51" s="1"/>
       <c r="G51" s="1"/>
     </row>
-    <row r="52" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B52" s="36" t="s">
+    <row r="52" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="B52" s="37" t="s">
         <v>36</v>
       </c>
-      <c r="C52" s="37"/>
+      <c r="C52" s="38"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1">
         <f>COUNTIF(G52:'song list'!END,"&lt;&gt;")</f>
@@ -1885,7 +1905,7 @@
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
     </row>
-    <row r="53" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B53" s="1">
         <v>1</v>
       </c>
@@ -1905,7 +1925,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="54" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B54" s="1">
         <v>2</v>
       </c>
@@ -1924,52 +1944,52 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
     </row>
-    <row r="56" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B56" s="1"/>
       <c r="F56" s="1"/>
       <c r="G56" s="1"/>
     </row>
-    <row r="57" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B57" s="1"/>
       <c r="F57" s="1"/>
       <c r="G57" s="1"/>
     </row>
-    <row r="58" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B58" s="1"/>
       <c r="F58" s="1"/>
       <c r="G58" s="1"/>
     </row>
-    <row r="59" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B59" s="1"/>
       <c r="F59" s="1"/>
       <c r="G59" s="1"/>
     </row>
-    <row r="60" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
     </row>
-    <row r="61" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="61" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B61" s="1"/>
       <c r="F61" s="1"/>
       <c r="G61" s="1"/>
     </row>
-    <row r="62" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B62" s="1"/>
       <c r="F62" s="1"/>
       <c r="G62" s="1"/>
     </row>
-    <row r="63" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B63" s="1"/>
       <c r="F63" s="1"/>
       <c r="G63" s="1"/>
     </row>
-    <row r="64" spans="2:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="2:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B64" s="1"/>
       <c r="F64" s="1"/>
       <c r="G64" s="1"/>
@@ -6786,6 +6806,7 @@
     <hyperlink ref="D24" r:id="rId30" xr:uid="{72810517-3CD0-5643-BFD6-2E9EE7C0EF4B}"/>
     <hyperlink ref="D16" r:id="rId31" xr:uid="{259F3BD9-4FE0-074B-BD50-3B5872B6B78E}"/>
     <hyperlink ref="D15" r:id="rId32" xr:uid="{FA8C1C39-EFA7-F046-815E-CD6C35742B9B}"/>
+    <hyperlink ref="D31" r:id="rId33" xr:uid="{9E881A86-1611-FE46-82E2-9CC134F32162}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D714519F-9A12-9140-8925-DFEC74A14A95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20250C6-7746-624D-8AB9-726A5C039BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-29220" yWindow="-3980" windowWidth="28540" windowHeight="19900" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32720" yWindow="-2760" windowWidth="25960" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
   <si>
     <t>Key</t>
   </si>
@@ -216,6 +216,12 @@
   </si>
   <si>
     <t>In Jesus Name (God of Possible)</t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Enough</t>
   </si>
 </sst>
 </file>
@@ -693,7 +699,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:AI1019"/>
+  <dimension ref="A2:AI1020"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
@@ -706,13 +712,12 @@
     <col min="14" max="15" width="5.5" style="5" bestFit="1" customWidth="1"/>
     <col min="16" max="18" width="6" style="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="5.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="6" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6" bestFit="1" customWidth="1"/>
-    <col min="24" max="26" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="6" bestFit="1" customWidth="1"/>
-    <col min="29" max="31" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="6" bestFit="1" customWidth="1"/>
-    <col min="33" max="35" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="6.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="31" width="6.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="6" style="5" bestFit="1" customWidth="1"/>
+    <col min="33" max="35" width="6.5" style="5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:35" ht="48" x14ac:dyDescent="0.15">
@@ -875,7 +880,7 @@
       <c r="C5" s="1"/>
       <c r="D5" s="1">
         <f>COUNTIF(F5:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1"/>
@@ -892,6 +897,9 @@
       <c r="T5" s="30">
         <v>2</v>
       </c>
+      <c r="W5" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="6" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
@@ -997,7 +1005,7 @@
       <c r="C10" s="1"/>
       <c r="D10" s="1">
         <f>COUNTIF(F10:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>2</v>
@@ -1007,162 +1015,182 @@
       </c>
       <c r="N10" s="19">
         <v>2</v>
+      </c>
+      <c r="W10" s="6">
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C11" s="1"/>
+      <c r="B11" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="35"/>
       <c r="D11" s="1">
         <f>COUNTIF(F11:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
+      <c r="O11" s="24"/>
+      <c r="S11" s="32"/>
     </row>
     <row r="12" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>42</v>
+      <c r="B12" s="2" t="s">
+        <v>44</v>
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
         <f>COUNTIF(F12:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" s="1"/>
       <c r="F12" s="1"/>
-      <c r="L12" s="24">
-        <v>1</v>
-      </c>
     </row>
     <row r="13" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="28" t="s">
-        <v>46</v>
+      <c r="B13" s="20" t="s">
+        <v>42</v>
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
         <f>COUNTIF(F13:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="26"/>
-      <c r="F13" s="26"/>
-      <c r="G13" s="26"/>
-      <c r="H13" s="26"/>
-      <c r="I13" s="26"/>
-      <c r="J13" s="26"/>
-      <c r="K13" s="26"/>
-      <c r="L13" s="26"/>
-      <c r="Q13" s="26"/>
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1"/>
+      <c r="L13" s="24">
+        <v>1</v>
+      </c>
+      <c r="W13" s="6">
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="20" t="s">
-        <v>7</v>
+      <c r="B14" s="28" t="s">
+        <v>46</v>
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
         <f>COUNTIF(F14:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E14" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F14" s="1"/>
-      <c r="G14" s="7">
-        <v>3</v>
-      </c>
-      <c r="Q14" s="7">
-        <v>3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" s="26"/>
+      <c r="F14" s="26"/>
+      <c r="G14" s="26"/>
+      <c r="H14" s="26"/>
+      <c r="I14" s="26"/>
+      <c r="J14" s="26"/>
+      <c r="K14" s="26"/>
+      <c r="L14" s="26"/>
+      <c r="Q14" s="26"/>
     </row>
     <row r="15" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="28" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>57</v>
-      </c>
+      <c r="B15" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="1"/>
       <c r="D15" s="1">
         <f>COUNTIF(F15:'song list'!END,"&lt;&gt;")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F15" s="11">
+      <c r="F15" s="1"/>
+      <c r="G15" s="7">
         <v>3</v>
       </c>
-      <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
-      <c r="J15" s="19">
-        <v>4</v>
-      </c>
+      <c r="J15" s="5"/>
       <c r="K15" s="5"/>
       <c r="L15" s="5"/>
-      <c r="M15" s="26"/>
-      <c r="N15" s="26"/>
-      <c r="O15" s="26"/>
-      <c r="P15" s="26"/>
-      <c r="Q15" s="5"/>
-      <c r="R15" s="31">
-        <v>2</v>
-      </c>
-      <c r="S15" s="26"/>
-      <c r="T15" s="26"/>
-      <c r="U15" s="36">
-        <v>4</v>
-      </c>
-      <c r="V15" s="26"/>
+      <c r="M15" s="5"/>
+      <c r="N15" s="5"/>
+      <c r="O15" s="5"/>
+      <c r="P15" s="5"/>
+      <c r="Q15" s="7">
+        <v>3</v>
+      </c>
+      <c r="R15" s="5"/>
+      <c r="S15" s="5"/>
+      <c r="T15" s="5"/>
+      <c r="U15" s="5"/>
+      <c r="V15" s="5"/>
+      <c r="W15" s="5"/>
+      <c r="X15" s="26"/>
+      <c r="Y15" s="26"/>
+      <c r="Z15" s="26"/>
+      <c r="AA15" s="26"/>
+      <c r="AB15" s="26"/>
+      <c r="AC15" s="26"/>
+      <c r="AD15" s="26"/>
+      <c r="AE15" s="26"/>
+      <c r="AF15" s="26"/>
+      <c r="AG15" s="26"/>
+      <c r="AH15" s="26"/>
+      <c r="AI15" s="26"/>
     </row>
     <row r="16" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>14</v>
       </c>
       <c r="B16" s="28" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="C16" s="35" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="1">
         <f>COUNTIF(F16:'song list'!END,"&lt;&gt;")</f>
+        <v>4</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F16" s="11">
+        <v>3</v>
+      </c>
+      <c r="J16" s="19">
+        <v>4</v>
+      </c>
+      <c r="M16" s="26"/>
+      <c r="N16" s="26"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="26"/>
+      <c r="R16" s="31">
         <v>2</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="30">
-        <v>1</v>
-      </c>
-      <c r="S16" s="32">
+      <c r="S16" s="26"/>
+      <c r="T16" s="26"/>
+      <c r="U16" s="36">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V16" s="26"/>
+      <c r="W16" s="26"/>
+    </row>
+    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
       <c r="B17" s="28" t="s">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="C17" s="35" t="s">
         <v>57</v>
@@ -1173,534 +1201,532 @@
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
-      <c r="O17" s="24">
+      <c r="G17" s="1"/>
+      <c r="Q17" s="1"/>
+      <c r="R17" s="30">
         <v>1</v>
       </c>
       <c r="S17" s="32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="20" t="s">
-        <v>20</v>
+      <c r="B18" s="28" t="s">
+        <v>17</v>
       </c>
       <c r="C18" s="35" t="s">
         <v>57</v>
       </c>
       <c r="D18" s="1">
         <f>COUNTIF(F18:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="G18" s="9">
-        <v>4</v>
-      </c>
-      <c r="H18" s="6">
+      <c r="O18" s="24">
+        <v>1</v>
+      </c>
+      <c r="S18" s="32">
         <v>3</v>
       </c>
-      <c r="Q18" s="9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="C19" s="1"/>
+      <c r="B19" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="D19" s="1">
         <f>COUNTIF(F19:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="Q19" s="1"/>
-    </row>
-    <row r="20" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G19" s="9">
+        <v>4</v>
+      </c>
+      <c r="H19" s="6">
+        <v>3</v>
+      </c>
+      <c r="Q19" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="28" t="s">
-        <v>10</v>
+        <v>49</v>
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
         <f>COUNTIF(F20:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-      <c r="K20" s="8">
-        <v>1</v>
-      </c>
-      <c r="T20" s="30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G20" s="1"/>
+      <c r="Q20" s="1"/>
+    </row>
+    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
       <c r="B21" s="28" t="s">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
         <f>COUNTIF(F21:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E21" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E21" s="1"/>
       <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="U21" s="7">
-        <v>3</v>
-      </c>
-      <c r="V21" s="32">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K21" s="8">
+        <v>1</v>
+      </c>
+      <c r="T21" s="30">
+        <v>1</v>
+      </c>
+      <c r="W21" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="20" t="s">
-        <v>8</v>
+      <c r="B22" s="28" t="s">
+        <v>50</v>
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
         <f>COUNTIF(F22:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E22" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F22" s="11">
-        <v>1</v>
-      </c>
-      <c r="T22" s="30">
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="Q22" s="1"/>
+      <c r="U22" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V22" s="32">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="28" t="s">
-        <v>53</v>
+      <c r="B23" s="20" t="s">
+        <v>8</v>
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f>COUNTIF(F23:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="Q23" s="1"/>
-    </row>
-    <row r="24" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F23" s="11">
+        <v>1</v>
+      </c>
+      <c r="T23" s="30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="28" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
         <f>COUNTIF(F24:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E24" s="1"/>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="Q24" s="1"/>
-      <c r="U24" s="7">
-        <v>2</v>
-      </c>
-      <c r="V24" s="32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
       <c r="B25" s="28" t="s">
-        <v>27</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>57</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C25" s="1"/>
       <c r="D25" s="1">
         <f>COUNTIF(F25:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="U25" s="7">
+        <v>2</v>
+      </c>
+      <c r="V25" s="32">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="28" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="C26" s="35" t="s">
         <v>57</v>
       </c>
       <c r="D26" s="1">
         <f>COUNTIF(F26:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="I26" s="8">
-        <v>1</v>
-      </c>
-      <c r="R26" s="30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="1"/>
+        <v>14</v>
+      </c>
+      <c r="C27" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="D27" s="1">
         <f>COUNTIF(F27:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="Q27" s="1"/>
-    </row>
-    <row r="28" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>2</v>
+      </c>
+      <c r="E27" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="I27" s="8">
+        <v>1</v>
+      </c>
+      <c r="R27" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
         <f>COUNTIF(F28:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
+      <c r="L28" s="12" t="s">
+        <v>60</v>
+      </c>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
       <c r="B29" s="28" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
         <f>COUNTIF(F29:'song list'!END,"&lt;&gt;")</f>
-        <v>5</v>
-      </c>
-      <c r="M29" s="7">
-        <v>3</v>
-      </c>
-      <c r="O29" s="24">
-        <v>4</v>
-      </c>
-      <c r="P29" s="29">
-        <v>1</v>
-      </c>
-      <c r="S29" s="32">
-        <v>2</v>
-      </c>
-      <c r="V29" s="32">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="Q29" s="1"/>
+    </row>
+    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>26</v>
+      <c r="B30" s="28" t="s">
+        <v>18</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
         <f>COUNTIF(F30:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="M30" s="7">
+        <v>3</v>
+      </c>
+      <c r="O30" s="24">
+        <v>4</v>
+      </c>
+      <c r="P30" s="29">
+        <v>1</v>
+      </c>
+      <c r="S30" s="32">
+        <v>2</v>
+      </c>
+      <c r="V30" s="32">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="28" t="s">
-        <v>45</v>
+      <c r="B31" s="2" t="s">
+        <v>26</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
         <f>COUNTIF(F31:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-    </row>
-    <row r="32" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
       <c r="B32" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>57</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="C32" s="1"/>
       <c r="D32" s="1">
         <f>COUNTIF(F32:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E32" s="1"/>
       <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="S32" s="32">
-        <v>1</v>
-      </c>
-      <c r="T32" s="30">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="1"/>
-      <c r="B33" s="2"/>
-      <c r="C33" s="1"/>
+    </row>
+    <row r="33" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>57</v>
+      </c>
       <c r="D33" s="1">
         <f>COUNTIF(F33:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B34" s="38"/>
+        <v>2</v>
+      </c>
+      <c r="E33" s="1"/>
+      <c r="F33" s="1"/>
+      <c r="G33" s="1"/>
+      <c r="Q33" s="1"/>
+      <c r="S33" s="32">
+        <v>1</v>
+      </c>
+      <c r="T33" s="30">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="34" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="1"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1">
         <f>COUNTIF(F34:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="1">
-        <v>1</v>
-      </c>
-      <c r="B35" s="20" t="s">
-        <v>32</v>
-      </c>
+    <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B35" s="38"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1">
         <f>COUNTIF(F35:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F35" s="1"/>
-      <c r="J35" s="19">
-        <v>5</v>
-      </c>
-      <c r="N35" s="19">
-        <v>5</v>
-      </c>
-      <c r="P35" s="29">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1">
-        <v>2</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>23</v>
+        <v>1</v>
+      </c>
+      <c r="B36" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="C36" s="1"/>
       <c r="D36" s="1">
         <f>COUNTIF(F36:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E36" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F36" s="1"/>
-    </row>
-    <row r="37" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J36" s="19">
+        <v>5</v>
+      </c>
+      <c r="N36" s="19">
+        <v>5</v>
+      </c>
+      <c r="P36" s="29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1">
-        <v>3</v>
-      </c>
-      <c r="B37" s="20" t="s">
-        <v>30</v>
+        <v>2</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
         <f>COUNTIF(F37:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E37" s="1"/>
       <c r="F37" s="1"/>
-      <c r="H37" s="6">
-        <v>5</v>
-      </c>
-      <c r="O37" s="24">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AB37" s="12" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="38" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A38" s="1">
-        <v>4</v>
-      </c>
-      <c r="B38" s="28" t="s">
-        <v>47</v>
+        <v>3</v>
+      </c>
+      <c r="B38" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <f>COUNTIF(F38:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" s="1"/>
       <c r="F38" s="1"/>
-      <c r="M38" s="7">
+      <c r="H38" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O38" s="24">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>5</v>
-      </c>
-      <c r="B39" s="20" t="s">
-        <v>12</v>
+        <v>4</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>47</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
         <f>COUNTIF(F39:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E39" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="E39" s="1"/>
       <c r="F39" s="1"/>
-      <c r="I39" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="M39" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B40" s="20" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
         <f>COUNTIF(F40:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F40" s="1"/>
       <c r="I40" s="8">
-        <v>5</v>
-      </c>
-      <c r="K40" s="8">
-        <v>4</v>
-      </c>
-      <c r="P40" s="29">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>7</v>
-      </c>
-      <c r="B41" s="28" t="s">
-        <v>51</v>
+        <v>6</v>
+      </c>
+      <c r="B41" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
         <f>COUNTIF(F41:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E41" s="26"/>
-      <c r="F41" s="26"/>
-      <c r="G41" s="26"/>
-      <c r="H41" s="26"/>
-      <c r="I41" s="26"/>
-      <c r="J41" s="26"/>
-      <c r="K41" s="26"/>
-      <c r="L41" s="26"/>
-      <c r="Q41" s="26"/>
-      <c r="V41" s="32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>3</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F41" s="1"/>
+      <c r="I41" s="8">
+        <v>5</v>
+      </c>
+      <c r="K41" s="8">
+        <v>4</v>
+      </c>
+      <c r="P41" s="29">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="42" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>8</v>
-      </c>
-      <c r="B42" s="20" t="s">
-        <v>22</v>
+        <v>7</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>51</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
         <f>COUNTIF(F42:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="E42" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F42" s="10">
+      <c r="E42" s="26"/>
+      <c r="F42" s="26"/>
+      <c r="G42" s="26"/>
+      <c r="H42" s="26"/>
+      <c r="I42" s="26"/>
+      <c r="J42" s="26"/>
+      <c r="K42" s="26"/>
+      <c r="L42" s="26"/>
+      <c r="Q42" s="26"/>
+      <c r="V42" s="32">
+        <v>1</v>
+      </c>
+      <c r="W42" s="6">
         <v>5</v>
       </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
-      <c r="I42" s="5"/>
-      <c r="J42" s="5"/>
-      <c r="K42" s="5"/>
-      <c r="L42" s="5"/>
-      <c r="M42" s="26"/>
-      <c r="N42" s="27">
-        <v>3</v>
-      </c>
-      <c r="O42" s="26"/>
-      <c r="P42" s="26"/>
-      <c r="Q42" s="5"/>
-      <c r="R42" s="26"/>
-      <c r="S42" s="33">
-        <v>5</v>
-      </c>
-      <c r="T42" s="26"/>
-      <c r="U42" s="26"/>
-      <c r="V42" s="26"/>
-    </row>
-    <row r="43" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="43" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>9</v>
-      </c>
-      <c r="B43" s="28" t="s">
-        <v>6</v>
+        <v>8</v>
+      </c>
+      <c r="B43" s="20" t="s">
+        <v>22</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
@@ -1708,198 +1734,239 @@
         <v>3</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F43" s="10">
-        <v>2</v>
-      </c>
-      <c r="L43" s="24">
         <v>5</v>
       </c>
-      <c r="R43" s="30">
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
+      <c r="L43" s="5"/>
+      <c r="M43" s="26"/>
+      <c r="N43" s="27">
+        <v>3</v>
+      </c>
+      <c r="O43" s="26"/>
+      <c r="P43" s="26"/>
+      <c r="Q43" s="5"/>
+      <c r="R43" s="26"/>
+      <c r="S43" s="33">
         <v>5</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="T43" s="26"/>
+      <c r="U43" s="26"/>
+      <c r="V43" s="26"/>
+      <c r="W43" s="26"/>
+      <c r="X43" s="26"/>
+      <c r="Y43" s="26"/>
+      <c r="Z43" s="26"/>
+      <c r="AA43" s="26"/>
+      <c r="AB43" s="26"/>
+      <c r="AC43" s="26"/>
+      <c r="AD43" s="26"/>
+      <c r="AE43" s="26"/>
+      <c r="AF43" s="26"/>
+      <c r="AG43" s="26"/>
+      <c r="AH43" s="26"/>
+      <c r="AI43" s="26"/>
+    </row>
+    <row r="44" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>10</v>
-      </c>
-      <c r="B44" s="20" t="s">
-        <v>29</v>
+        <v>9</v>
+      </c>
+      <c r="B44" s="28" t="s">
+        <v>6</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
         <f>COUNTIF(F44:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F44" s="10">
         <v>2</v>
       </c>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="H44" s="6">
-        <v>4</v>
-      </c>
       <c r="L44" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="R44" s="30">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B45" s="20" t="s">
-        <v>5</v>
+        <v>29</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
         <f>COUNTIF(F45:'song list'!END,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
+      <c r="H45" s="6">
+        <v>4</v>
+      </c>
+      <c r="L45" s="24">
         <v>3</v>
       </c>
-      <c r="E45" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F45" s="1"/>
-      <c r="G45" s="7">
+    </row>
+    <row r="46" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A46" s="1">
+        <v>11</v>
+      </c>
+      <c r="B46" s="20" t="s">
         <v>5</v>
-      </c>
-      <c r="K45" s="8">
-        <v>5</v>
-      </c>
-      <c r="Q45" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="1">
-        <v>12</v>
-      </c>
-      <c r="B46" s="20" t="s">
-        <v>15</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
         <f>COUNTIF(F46:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F46" s="1"/>
-      <c r="J46" s="19">
-        <v>3</v>
+      <c r="G46" s="7">
+        <v>5</v>
       </c>
       <c r="K46" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <v>5</v>
+      </c>
+      <c r="Q46" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B47" s="20" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
         <f>COUNTIF(F47:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F47" s="1"/>
-      <c r="H47" s="6">
-        <v>2</v>
-      </c>
-      <c r="M47" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J47" s="19">
+        <v>3</v>
+      </c>
+      <c r="K47" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="48" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
         <f>COUNTIF(F48:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
-      <c r="G48" s="7">
-        <v>1</v>
-      </c>
-      <c r="L48" s="23">
+      <c r="H48" s="6">
         <v>2</v>
       </c>
-      <c r="Q48" s="7">
-        <v>1</v>
+      <c r="M48" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>15</v>
-      </c>
-      <c r="B49" s="22" t="s">
-        <v>25</v>
+        <v>14</v>
+      </c>
+      <c r="B49" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
         <f>COUNTIF(F49:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E49" s="1"/>
+      <c r="F49" s="1"/>
+      <c r="G49" s="7">
+        <v>1</v>
+      </c>
+      <c r="L49" s="23">
         <v>2</v>
       </c>
-      <c r="E49" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F49" s="1"/>
-      <c r="K49" s="8">
-        <v>2</v>
-      </c>
-      <c r="L49" s="25"/>
-      <c r="O49" s="24">
-        <v>5</v>
+      <c r="Q49" s="7">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
-        <v>16</v>
-      </c>
-      <c r="B50" s="28" t="s">
-        <v>56</v>
+        <v>15</v>
+      </c>
+      <c r="B50" s="22" t="s">
+        <v>25</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
         <f>COUNTIF(F50:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F50" s="1"/>
-      <c r="J50" s="19"/>
-      <c r="K50" s="8"/>
-      <c r="T50" s="30">
-        <v>5</v>
-      </c>
-      <c r="V50" s="32">
+      <c r="K50" s="8">
+        <v>2</v>
+      </c>
+      <c r="L50" s="25"/>
+      <c r="O50" s="24">
         <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B51" s="28" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
         <f>COUNTIF(F51:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
+      <c r="J51" s="19"/>
+      <c r="K51" s="8"/>
+      <c r="T51" s="30">
+        <v>5</v>
+      </c>
+      <c r="V51" s="32">
+        <v>5</v>
+      </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="1"/>
-      <c r="B52" s="4"/>
+      <c r="A52" s="1">
+        <v>17</v>
+      </c>
+      <c r="B52" s="28" t="s">
+        <v>24</v>
+      </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
         <f>COUNTIF(F52:'song list'!END,"&lt;&gt;")</f>
@@ -1909,10 +1976,8 @@
       <c r="F52" s="1"/>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B53" s="38"/>
+      <c r="A53" s="1"/>
+      <c r="B53" s="4"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
         <f>COUNTIF(F53:'song list'!END,"&lt;&gt;")</f>
@@ -1922,32 +1987,26 @@
       <c r="F53" s="1"/>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="1">
-        <v>1</v>
-      </c>
-      <c r="B54" s="20" t="s">
-        <v>31</v>
-      </c>
+      <c r="A54" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54" s="38"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
         <f>COUNTIF(F54:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="I54" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B55" s="20" t="s">
-        <v>38</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C55" s="1"/>
       <c r="D55" s="1">
         <f>COUNTIF(F55:'song list'!END,"&lt;&gt;")</f>
         <v>1</v>
@@ -1956,14 +2015,28 @@
         <v>2</v>
       </c>
       <c r="F55" s="1"/>
-      <c r="J55" s="19">
+      <c r="I55" s="8">
         <v>2</v>
       </c>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="1"/>
-      <c r="E56" s="1"/>
+      <c r="A56" s="1">
+        <v>2</v>
+      </c>
+      <c r="B56" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D56" s="1">
+        <f>COUNTIF(F56:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="E56" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F56" s="1"/>
+      <c r="J56" s="19">
+        <v>2</v>
+      </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1"/>
@@ -2205,7 +2278,7 @@
       <c r="E104" s="1"/>
       <c r="F104" s="1"/>
     </row>
-    <row r="105" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="105" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A105" s="1"/>
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
@@ -6780,49 +6853,55 @@
       <c r="E1019" s="1"/>
       <c r="F1019" s="1"/>
     </row>
+    <row r="1020" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1020" s="1"/>
+      <c r="E1020" s="1"/>
+      <c r="F1020" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B35:U51">
-    <sortCondition ref="B35:B51"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:W33">
+    <sortCondition ref="B4:B33"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A53:B53"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A54:B54"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="B13" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
-    <hyperlink ref="B31" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="B38" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="B51" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
-    <hyperlink ref="B16" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
-    <hyperlink ref="B19" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
-    <hyperlink ref="B21" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="B41" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
-    <hyperlink ref="B27" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
+    <hyperlink ref="B14" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
+    <hyperlink ref="B30" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
+    <hyperlink ref="B32" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
+    <hyperlink ref="B39" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="B52" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="B17" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
+    <hyperlink ref="B20" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
+    <hyperlink ref="B22" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
+    <hyperlink ref="B42" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="B28" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="B7" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
-    <hyperlink ref="B25" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
+    <hyperlink ref="B26" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="B5" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
-    <hyperlink ref="B26" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
-    <hyperlink ref="B15" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="B43" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
-    <hyperlink ref="B32" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
+    <hyperlink ref="B27" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
+    <hyperlink ref="B16" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
+    <hyperlink ref="B44" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="B33" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
     <hyperlink ref="B9" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
     <hyperlink ref="B10" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
-    <hyperlink ref="B28" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
-    <hyperlink ref="B17" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
-    <hyperlink ref="B23" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
-    <hyperlink ref="B50" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
-    <hyperlink ref="B20" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
+    <hyperlink ref="B29" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
+    <hyperlink ref="B18" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
+    <hyperlink ref="B24" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
+    <hyperlink ref="B51" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="B21" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
     <hyperlink ref="C9" r:id="rId25" xr:uid="{93134F2E-198C-D74C-8193-8EFB343FFEA8}"/>
-    <hyperlink ref="C26" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
-    <hyperlink ref="C18" r:id="rId27" xr:uid="{2B2EFF17-7C8B-7E47-99BF-2437146F3F4A}"/>
-    <hyperlink ref="C15" r:id="rId28" xr:uid="{8FEF4FFD-A276-7946-98B4-C48564B7D962}"/>
+    <hyperlink ref="C27" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
+    <hyperlink ref="C19" r:id="rId27" xr:uid="{2B2EFF17-7C8B-7E47-99BF-2437146F3F4A}"/>
+    <hyperlink ref="C16" r:id="rId28" xr:uid="{8FEF4FFD-A276-7946-98B4-C48564B7D962}"/>
     <hyperlink ref="C8" r:id="rId29" xr:uid="{7F154C3C-C716-3646-BC29-496637A29377}"/>
-    <hyperlink ref="C25" r:id="rId30" xr:uid="{72810517-3CD0-5643-BFD6-2E9EE7C0EF4B}"/>
-    <hyperlink ref="C17" r:id="rId31" xr:uid="{259F3BD9-4FE0-074B-BD50-3B5872B6B78E}"/>
-    <hyperlink ref="C16" r:id="rId32" xr:uid="{FA8C1C39-EFA7-F046-815E-CD6C35742B9B}"/>
-    <hyperlink ref="C32" r:id="rId33" xr:uid="{9E881A86-1611-FE46-82E2-9CC134F32162}"/>
+    <hyperlink ref="C26" r:id="rId30" xr:uid="{72810517-3CD0-5643-BFD6-2E9EE7C0EF4B}"/>
+    <hyperlink ref="C18" r:id="rId31" xr:uid="{259F3BD9-4FE0-074B-BD50-3B5872B6B78E}"/>
+    <hyperlink ref="C17" r:id="rId32" xr:uid="{FA8C1C39-EFA7-F046-815E-CD6C35742B9B}"/>
+    <hyperlink ref="C33" r:id="rId33" xr:uid="{9E881A86-1611-FE46-82E2-9CC134F32162}"/>
+    <hyperlink ref="B11" r:id="rId34" xr:uid="{646C8938-F9C4-8349-9383-8BF3C536D75D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F20250C6-7746-624D-8AB9-726A5C039BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C71B6C-7C80-B84D-92C9-DD83C76E3638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32720" yWindow="-2760" windowWidth="25960" windowHeight="19660" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-32200" yWindow="-3980" windowWidth="28340" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="87" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
   <si>
     <t>Key</t>
   </si>
@@ -218,10 +218,10 @@
     <t>In Jesus Name (God of Possible)</t>
   </si>
   <si>
-    <t>s</t>
+    <t>Enough</t>
   </si>
   <si>
-    <t>Enough</t>
+    <t>I Surrender All</t>
   </si>
 </sst>
 </file>
@@ -376,7 +376,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -479,6 +479,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -699,13 +702,13 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:AI1020"/>
+  <dimension ref="A2:AI1026"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
     <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.1640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="5.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" style="5" customWidth="1"/>
     <col min="5" max="5" width="3.83203125" style="5" customWidth="1"/>
     <col min="6" max="11" width="5.5" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="6" style="5" bestFit="1" customWidth="1"/>
@@ -850,8 +853,8 @@
       </c>
       <c r="C4" s="1"/>
       <c r="D4" s="1">
-        <f>COUNTIF(F4:'song list'!END,"&lt;&gt;")</f>
-        <v>4</v>
+        <f>COUNTIF(F4:AI4,"&lt;&gt;")</f>
+        <v>5</v>
       </c>
       <c r="E4" s="12" t="s">
         <v>41</v>
@@ -869,6 +872,9 @@
       <c r="U4" s="7">
         <v>5</v>
       </c>
+      <c r="X4" s="7">
+        <v>5</v>
+      </c>
     </row>
     <row r="5" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
@@ -879,7 +885,7 @@
       </c>
       <c r="C5" s="1"/>
       <c r="D5" s="1">
-        <f>COUNTIF(F5:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F5:AI5,"&lt;&gt;")</f>
         <v>4</v>
       </c>
       <c r="E5" s="1"/>
@@ -910,7 +916,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
-        <f>COUNTIF(F6:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" ref="D6:D33" si="0">COUNTIF(F6:AI6,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="E6" s="1"/>
@@ -925,7 +931,7 @@
       </c>
       <c r="C7" s="1"/>
       <c r="D7" s="1">
-        <f>COUNTIF(F7:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E7" s="1"/>
@@ -948,7 +954,7 @@
         <v>57</v>
       </c>
       <c r="D8" s="1">
-        <f>COUNTIF(F8:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E8" s="12" t="s">
@@ -978,7 +984,7 @@
         <v>57</v>
       </c>
       <c r="D9" s="1">
-        <f>COUNTIF(F9:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1004,7 +1010,7 @@
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1">
-        <f>COUNTIF(F10:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1025,11 +1031,11 @@
         <v>9</v>
       </c>
       <c r="B11" s="28" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C11" s="35"/>
       <c r="D11" s="1">
-        <f>COUNTIF(F11:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E11" s="1"/>
@@ -1046,7 +1052,7 @@
       </c>
       <c r="C12" s="1"/>
       <c r="D12" s="1">
-        <f>COUNTIF(F12:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E12" s="1"/>
@@ -1061,7 +1067,7 @@
       </c>
       <c r="C13" s="1"/>
       <c r="D13" s="1">
-        <f>COUNTIF(F13:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1084,7 +1090,7 @@
       </c>
       <c r="C14" s="1"/>
       <c r="D14" s="1">
-        <f>COUNTIF(F14:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E14" s="26"/>
@@ -1106,7 +1112,7 @@
       </c>
       <c r="C15" s="1"/>
       <c r="D15" s="1">
-        <f>COUNTIF(F15:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -1158,7 +1164,7 @@
         <v>57</v>
       </c>
       <c r="D16" s="1">
-        <f>COUNTIF(F16:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -1185,7 +1191,7 @@
       <c r="V16" s="26"/>
       <c r="W16" s="26"/>
     </row>
-    <row r="17" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>57</v>
       </c>
       <c r="D17" s="1">
-        <f>COUNTIF(F17:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E17" s="1"/>
@@ -1210,7 +1216,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1221,8 +1227,8 @@
         <v>57</v>
       </c>
       <c r="D18" s="1">
-        <f>COUNTIF(F18:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
@@ -1232,8 +1238,11 @@
       <c r="S18" s="32">
         <v>3</v>
       </c>
-    </row>
-    <row r="19" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X18" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1244,7 +1253,7 @@
         <v>57</v>
       </c>
       <c r="D19" s="1">
-        <f>COUNTIF(F19:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E19" s="1"/>
@@ -1259,7 +1268,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1268,7 +1277,7 @@
       </c>
       <c r="C20" s="1"/>
       <c r="D20" s="1">
-        <f>COUNTIF(F20:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E20" s="1"/>
@@ -1276,7 +1285,7 @@
       <c r="G20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1285,7 +1294,7 @@
       </c>
       <c r="C21" s="1"/>
       <c r="D21" s="1">
-        <f>COUNTIF(F21:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -1302,7 +1311,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1311,8 +1320,8 @@
       </c>
       <c r="C22" s="1"/>
       <c r="D22" s="1">
-        <f>COUNTIF(F22:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="1"/>
@@ -1324,8 +1333,11 @@
       <c r="V22" s="32">
         <v>2</v>
       </c>
-    </row>
-    <row r="23" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="X22" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1334,7 +1346,7 @@
       </c>
       <c r="C23" s="1"/>
       <c r="D23" s="1">
-        <f>COUNTIF(F23:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -1347,7 +1359,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1356,7 +1368,7 @@
       </c>
       <c r="C24" s="1"/>
       <c r="D24" s="1">
-        <f>COUNTIF(F24:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E24" s="1"/>
@@ -1364,7 +1376,7 @@
       <c r="G24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1373,7 +1385,7 @@
       </c>
       <c r="C25" s="1"/>
       <c r="D25" s="1">
-        <f>COUNTIF(F25:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E25" s="1"/>
@@ -1387,7 +1399,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1398,11 +1410,11 @@
         <v>57</v>
       </c>
       <c r="D26" s="1">
-        <f>COUNTIF(F26:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1413,7 +1425,7 @@
         <v>57</v>
       </c>
       <c r="D27" s="1">
-        <f>COUNTIF(F27:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -1426,7 +1438,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1435,18 +1447,16 @@
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1">
-        <f>COUNTIF(F28:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="E28" s="1"/>
       <c r="F28" s="1"/>
       <c r="G28" s="1"/>
-      <c r="L28" s="12" t="s">
-        <v>60</v>
-      </c>
+      <c r="L28" s="12"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1455,7 +1465,7 @@
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1">
-        <f>COUNTIF(F29:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E29" s="1"/>
@@ -1463,7 +1473,7 @@
       <c r="G29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1472,7 +1482,7 @@
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
-        <f>COUNTIF(F30:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="M30" s="7">
@@ -1491,20 +1501,26 @@
         <v>3</v>
       </c>
     </row>
-    <row r="31" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="2" t="s">
+      <c r="B31" s="28" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
-        <f>COUNTIF(F31:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E31" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="X31" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1513,11 +1529,16 @@
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1">
-        <f>COUNTIF(F32:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="1"/>
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="F32" s="1"/>
+      <c r="X32" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="33" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="1">
@@ -1530,7 +1551,7 @@
         <v>57</v>
       </c>
       <c r="D33" s="1">
-        <f>COUNTIF(F33:'song list'!END,"&lt;&gt;")</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="E33" s="1"/>
@@ -1546,239 +1567,167 @@
     </row>
     <row r="34" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
-      <c r="B34" s="2"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1">
-        <f>COUNTIF(F34:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="B34" s="28"/>
+      <c r="C34" s="35"/>
+      <c r="D34" s="1"/>
+      <c r="E34" s="1"/>
+      <c r="F34" s="1"/>
+      <c r="G34" s="1"/>
+      <c r="Q34" s="1"/>
+      <c r="S34" s="39"/>
+      <c r="T34" s="39"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="37" t="s">
-        <v>35</v>
-      </c>
-      <c r="B35" s="38"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1">
-        <f>COUNTIF(F35:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="A35" s="1"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="35"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
+      <c r="G35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="S35" s="39"/>
+      <c r="T35" s="39"/>
     </row>
     <row r="36" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="1">
-        <v>1</v>
-      </c>
-      <c r="B36" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1">
-        <f>COUNTIF(F36:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="E36" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="A36" s="1"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="35"/>
+      <c r="D36" s="1"/>
+      <c r="E36" s="1"/>
       <c r="F36" s="1"/>
-      <c r="J36" s="19">
-        <v>5</v>
-      </c>
-      <c r="N36" s="19">
-        <v>5</v>
-      </c>
-      <c r="P36" s="29">
-        <v>5</v>
-      </c>
+      <c r="G36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="S36" s="39"/>
+      <c r="T36" s="39"/>
     </row>
     <row r="37" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="1">
-        <v>2</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>23</v>
-      </c>
+      <c r="A37" s="1"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1">
         <f>COUNTIF(F37:'song list'!END,"&lt;&gt;")</f>
         <v>0</v>
       </c>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="AB37" s="12" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="38" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="1">
-        <v>3</v>
-      </c>
-      <c r="B38" s="20" t="s">
-        <v>30</v>
-      </c>
+      <c r="A38" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="B38" s="38"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <f>COUNTIF(F38:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="H38" s="6">
-        <v>5</v>
-      </c>
-      <c r="O38" s="24">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="1">
-        <v>4</v>
-      </c>
-      <c r="B39" s="28" t="s">
-        <v>47</v>
+        <v>1</v>
+      </c>
+      <c r="B39" s="20" t="s">
+        <v>32</v>
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
         <f>COUNTIF(F39:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E39" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F39" s="1"/>
-      <c r="M39" s="7">
+      <c r="J39" s="19">
+        <v>5</v>
+      </c>
+      <c r="N39" s="19">
+        <v>5</v>
+      </c>
+      <c r="P39" s="29">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A40" s="1">
-        <v>5</v>
-      </c>
-      <c r="B40" s="20" t="s">
-        <v>12</v>
+        <v>2</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
         <f>COUNTIF(F40:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E40" s="1" t="s">
-        <v>11</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E40" s="1"/>
       <c r="F40" s="1"/>
-      <c r="I40" s="8">
-        <v>3</v>
-      </c>
+      <c r="AB40" s="12"/>
     </row>
     <row r="41" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B41" s="20" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
         <f>COUNTIF(F41:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="E41" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="I41" s="8">
+      <c r="H41" s="6">
         <v>5</v>
       </c>
-      <c r="K41" s="8">
-        <v>4</v>
-      </c>
-      <c r="P41" s="29">
-        <v>4</v>
+      <c r="O41" s="24">
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="B42" s="28" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
         <f>COUNTIF(F42:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
-      </c>
-      <c r="E42" s="26"/>
-      <c r="F42" s="26"/>
-      <c r="G42" s="26"/>
-      <c r="H42" s="26"/>
-      <c r="I42" s="26"/>
-      <c r="J42" s="26"/>
-      <c r="K42" s="26"/>
-      <c r="L42" s="26"/>
-      <c r="Q42" s="26"/>
-      <c r="V42" s="32">
         <v>1</v>
       </c>
-      <c r="W42" s="6">
+      <c r="E42" s="1"/>
+      <c r="F42" s="1"/>
+      <c r="M42" s="7">
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B43" s="20" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
         <f>COUNTIF(F43:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F43" s="1"/>
+      <c r="I43" s="8">
         <v>3</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F43" s="10">
-        <v>5</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
-      <c r="L43" s="5"/>
-      <c r="M43" s="26"/>
-      <c r="N43" s="27">
-        <v>3</v>
-      </c>
-      <c r="O43" s="26"/>
-      <c r="P43" s="26"/>
-      <c r="Q43" s="5"/>
-      <c r="R43" s="26"/>
-      <c r="S43" s="33">
-        <v>5</v>
-      </c>
-      <c r="T43" s="26"/>
-      <c r="U43" s="26"/>
-      <c r="V43" s="26"/>
-      <c r="W43" s="26"/>
-      <c r="X43" s="26"/>
-      <c r="Y43" s="26"/>
-      <c r="Z43" s="26"/>
-      <c r="AA43" s="26"/>
-      <c r="AB43" s="26"/>
-      <c r="AC43" s="26"/>
-      <c r="AD43" s="26"/>
-      <c r="AE43" s="26"/>
-      <c r="AF43" s="26"/>
-      <c r="AG43" s="26"/>
-      <c r="AH43" s="26"/>
-      <c r="AI43" s="26"/>
     </row>
     <row r="44" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A44" s="1">
-        <v>9</v>
-      </c>
-      <c r="B44" s="28" t="s">
         <v>6</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
@@ -1786,45 +1735,53 @@
         <v>3</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F44" s="1"/>
+      <c r="I44" s="8">
+        <v>5</v>
+      </c>
+      <c r="K44" s="8">
         <v>4</v>
       </c>
-      <c r="F44" s="10">
-        <v>2</v>
-      </c>
-      <c r="L44" s="24">
-        <v>5</v>
-      </c>
-      <c r="R44" s="30">
-        <v>5</v>
+      <c r="P44" s="29">
+        <v>4</v>
       </c>
     </row>
     <row r="45" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
-        <v>10</v>
-      </c>
-      <c r="B45" s="20" t="s">
-        <v>29</v>
+        <v>7</v>
+      </c>
+      <c r="B45" s="28" t="s">
+        <v>51</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
         <f>COUNTIF(F45:'song list'!END,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="H45" s="6">
-        <v>4</v>
-      </c>
-      <c r="L45" s="24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="46" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="E45" s="26"/>
+      <c r="F45" s="26"/>
+      <c r="G45" s="26"/>
+      <c r="H45" s="26"/>
+      <c r="I45" s="26"/>
+      <c r="J45" s="26"/>
+      <c r="K45" s="26"/>
+      <c r="L45" s="26"/>
+      <c r="Q45" s="26"/>
+      <c r="V45" s="32">
+        <v>1</v>
+      </c>
+      <c r="W45" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B46" s="20" t="s">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="C46" s="1"/>
       <c r="D46" s="1">
@@ -1834,46 +1791,74 @@
       <c r="E46" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F46" s="1"/>
-      <c r="G46" s="7">
+      <c r="F46" s="10">
         <v>5</v>
       </c>
-      <c r="K46" s="8">
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+      <c r="I46" s="5"/>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5"/>
+      <c r="L46" s="5"/>
+      <c r="M46" s="26"/>
+      <c r="N46" s="27">
+        <v>3</v>
+      </c>
+      <c r="O46" s="26"/>
+      <c r="P46" s="26"/>
+      <c r="Q46" s="5"/>
+      <c r="R46" s="26"/>
+      <c r="S46" s="33">
         <v>5</v>
       </c>
-      <c r="Q46" s="7">
-        <v>5</v>
-      </c>
+      <c r="T46" s="26"/>
+      <c r="U46" s="26"/>
+      <c r="V46" s="26"/>
+      <c r="W46" s="26"/>
+      <c r="X46" s="26"/>
+      <c r="Y46" s="26"/>
+      <c r="Z46" s="26"/>
+      <c r="AA46" s="26"/>
+      <c r="AB46" s="26"/>
+      <c r="AC46" s="26"/>
+      <c r="AD46" s="26"/>
+      <c r="AE46" s="26"/>
+      <c r="AF46" s="26"/>
+      <c r="AG46" s="26"/>
+      <c r="AH46" s="26"/>
+      <c r="AI46" s="26"/>
     </row>
     <row r="47" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
-        <v>12</v>
-      </c>
-      <c r="B47" s="20" t="s">
-        <v>15</v>
+        <v>9</v>
+      </c>
+      <c r="B47" s="28" t="s">
+        <v>6</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
         <f>COUNTIF(F47:'song list'!END,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F47" s="10">
         <v>2</v>
       </c>
-      <c r="E47" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="J47" s="19">
-        <v>3</v>
-      </c>
-      <c r="K47" s="8">
-        <v>3</v>
+      <c r="L47" s="24">
+        <v>5</v>
+      </c>
+      <c r="R47" s="30">
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
@@ -1883,42 +1868,44 @@
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="H48" s="6">
-        <v>2</v>
-      </c>
-      <c r="M48" s="7">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="L48" s="24">
+        <v>3</v>
       </c>
     </row>
     <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B49" s="20" t="s">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
         <f>COUNTIF(F49:'song list'!END,"&lt;&gt;")</f>
         <v>3</v>
       </c>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F49" s="1"/>
       <c r="G49" s="7">
-        <v>1</v>
-      </c>
-      <c r="L49" s="23">
-        <v>2</v>
+        <v>5</v>
+      </c>
+      <c r="K49" s="8">
+        <v>5</v>
       </c>
       <c r="Q49" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
+        <v>12</v>
+      </c>
+      <c r="B50" s="20" t="s">
         <v>15</v>
-      </c>
-      <c r="B50" s="22" t="s">
-        <v>25</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
@@ -1929,20 +1916,19 @@
         <v>2</v>
       </c>
       <c r="F50" s="1"/>
+      <c r="J50" s="19">
+        <v>3</v>
+      </c>
       <c r="K50" s="8">
-        <v>2</v>
-      </c>
-      <c r="L50" s="25"/>
-      <c r="O50" s="24">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="51" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
-        <v>16</v>
-      </c>
-      <c r="B51" s="28" t="s">
-        <v>56</v>
+        <v>13</v>
+      </c>
+      <c r="B51" s="20" t="s">
+        <v>19</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
@@ -1951,122 +1937,189 @@
       </c>
       <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="J51" s="19"/>
-      <c r="K51" s="8"/>
-      <c r="T51" s="30">
-        <v>5</v>
-      </c>
-      <c r="V51" s="32">
-        <v>5</v>
+      <c r="H51" s="6">
+        <v>2</v>
+      </c>
+      <c r="M51" s="7">
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
-        <v>17</v>
-      </c>
-      <c r="B52" s="28" t="s">
-        <v>24</v>
+        <v>14</v>
+      </c>
+      <c r="B52" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
         <f>COUNTIF(F52:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
+      <c r="G52" s="7">
+        <v>1</v>
+      </c>
+      <c r="L52" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q52" s="7">
+        <v>1</v>
+      </c>
     </row>
     <row r="53" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="1"/>
-      <c r="B53" s="4"/>
+      <c r="A53" s="1">
+        <v>15</v>
+      </c>
+      <c r="B53" s="22" t="s">
+        <v>25</v>
+      </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
         <f>COUNTIF(F53:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E53" s="1"/>
+        <v>2</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F53" s="1"/>
+      <c r="K53" s="8">
+        <v>2</v>
+      </c>
+      <c r="L53" s="25"/>
+      <c r="O53" s="24">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B54" s="38"/>
+      <c r="A54" s="1">
+        <v>16</v>
+      </c>
+      <c r="B54" s="28" t="s">
+        <v>56</v>
+      </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
         <f>COUNTIF(F54:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
+      <c r="J54" s="19"/>
+      <c r="K54" s="8"/>
+      <c r="T54" s="30">
+        <v>5</v>
+      </c>
+      <c r="V54" s="32">
+        <v>5</v>
+      </c>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
-        <v>1</v>
-      </c>
-      <c r="B55" s="20" t="s">
-        <v>31</v>
+        <v>17</v>
+      </c>
+      <c r="B55" s="28" t="s">
+        <v>24</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
         <f>COUNTIF(F55:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E55" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" s="1"/>
       <c r="F55" s="1"/>
-      <c r="I55" s="8">
-        <v>2</v>
-      </c>
     </row>
     <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
-        <v>2</v>
-      </c>
-      <c r="B56" s="20" t="s">
-        <v>38</v>
-      </c>
-      <c r="D56" s="1">
-        <f>COUNTIF(F56:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
-      </c>
-      <c r="E56" s="1" t="s">
-        <v>2</v>
-      </c>
+        <v>18</v>
+      </c>
+      <c r="B56" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-      <c r="J56" s="19">
-        <v>2</v>
-      </c>
     </row>
     <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
     <row r="58" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
     <row r="59" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1"/>
+      <c r="B59" s="4"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1">
+        <f>COUNTIF(F59:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
     <row r="60" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="1"/>
+      <c r="A60" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="B60" s="38"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1">
+        <f>COUNTIF(F60:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="1"/>
-      <c r="E61" s="1"/>
+      <c r="A61" s="1">
+        <v>1</v>
+      </c>
+      <c r="B61" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1">
+        <f>COUNTIF(F61:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F61" s="1"/>
+      <c r="I61" s="8">
+        <v>2</v>
+      </c>
     </row>
     <row r="62" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="1"/>
-      <c r="E62" s="1"/>
+      <c r="A62" s="1">
+        <v>2</v>
+      </c>
+      <c r="B62" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D62" s="1">
+        <f>COUNTIF(F62:'song list'!END,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F62" s="1"/>
+      <c r="J62" s="19">
+        <v>2</v>
+      </c>
     </row>
     <row r="63" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="1"/>
@@ -2283,32 +2336,32 @@
       <c r="E105" s="1"/>
       <c r="F105" s="1"/>
     </row>
-    <row r="106" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="106" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A106" s="1"/>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
     </row>
-    <row r="107" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="107" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A107" s="1"/>
       <c r="E107" s="1"/>
       <c r="F107" s="1"/>
     </row>
-    <row r="108" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="108" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
     </row>
-    <row r="109" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="109" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A109" s="1"/>
       <c r="E109" s="1"/>
       <c r="F109" s="1"/>
     </row>
-    <row r="110" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="110" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A110" s="1"/>
       <c r="E110" s="1"/>
       <c r="F110" s="1"/>
     </row>
-    <row r="111" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="111" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A111" s="1"/>
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
@@ -6857,6 +6910,36 @@
       <c r="A1020" s="1"/>
       <c r="E1020" s="1"/>
       <c r="F1020" s="1"/>
+    </row>
+    <row r="1021" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1021" s="1"/>
+      <c r="E1021" s="1"/>
+      <c r="F1021" s="1"/>
+    </row>
+    <row r="1022" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1022" s="1"/>
+      <c r="E1022" s="1"/>
+      <c r="F1022" s="1"/>
+    </row>
+    <row r="1023" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1023" s="1"/>
+      <c r="E1023" s="1"/>
+      <c r="F1023" s="1"/>
+    </row>
+    <row r="1024" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1024" s="1"/>
+      <c r="E1024" s="1"/>
+      <c r="F1024" s="1"/>
+    </row>
+    <row r="1025" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1025" s="1"/>
+      <c r="E1025" s="1"/>
+      <c r="F1025" s="1"/>
+    </row>
+    <row r="1026" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1026" s="1"/>
+      <c r="E1026" s="1"/>
+      <c r="F1026" s="1"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:W33">
@@ -6864,33 +6947,33 @@
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A54:B54"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A60:B60"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B14" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
     <hyperlink ref="B30" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
     <hyperlink ref="B32" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="B39" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="B52" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="B42" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="B55" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="B17" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="B20" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="B22" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="B42" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="B45" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="B28" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="B7" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
     <hyperlink ref="B26" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="B5" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
     <hyperlink ref="B27" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
     <hyperlink ref="B16" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="B44" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="B47" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
     <hyperlink ref="B33" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
     <hyperlink ref="B9" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
     <hyperlink ref="B10" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
     <hyperlink ref="B29" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
     <hyperlink ref="B18" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
     <hyperlink ref="B24" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
-    <hyperlink ref="B51" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="B54" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
     <hyperlink ref="B21" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
     <hyperlink ref="C9" r:id="rId25" xr:uid="{93134F2E-198C-D74C-8193-8EFB343FFEA8}"/>
     <hyperlink ref="C27" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
@@ -6902,6 +6985,7 @@
     <hyperlink ref="C17" r:id="rId32" xr:uid="{FA8C1C39-EFA7-F046-815E-CD6C35742B9B}"/>
     <hyperlink ref="C33" r:id="rId33" xr:uid="{9E881A86-1611-FE46-82E2-9CC134F32162}"/>
     <hyperlink ref="B11" r:id="rId34" xr:uid="{646C8938-F9C4-8349-9383-8BF3C536D75D}"/>
+    <hyperlink ref="B31" r:id="rId35" xr:uid="{B242CBB2-6F0F-B946-B48D-BB7DF3D3B30E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C71B6C-7C80-B84D-92C9-DD83C76E3638}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DBCE9E-215A-2447-A502-1AA9950D0F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32200" yWindow="-3980" windowWidth="28340" windowHeight="19180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3860" yWindow="600" windowWidth="16500" windowHeight="26140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
   <si>
     <t>Key</t>
   </si>
@@ -223,12 +223,18 @@
   <si>
     <t>I Surrender All</t>
   </si>
+  <si>
+    <t>Blessed Assurance</t>
+  </si>
+  <si>
+    <t>C,D</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -279,12 +285,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial (Body)"/>
     </font>
     <font>
       <u/>
@@ -374,9 +374,9 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -433,7 +433,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -449,7 +448,7 @@
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -462,13 +461,10 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -481,6 +477,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -702,14 +701,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A2:AI1026"/>
+  <dimension ref="A2:AI1027"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="5.5" customWidth="1"/>
     <col min="2" max="2" width="30.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.1640625" style="12" customWidth="1"/>
-    <col min="4" max="4" width="8.83203125" style="5" customWidth="1"/>
-    <col min="5" max="5" width="3.83203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="4.6640625" style="5" customWidth="1"/>
+    <col min="5" max="5" width="6.33203125" style="5" customWidth="1"/>
     <col min="6" max="11" width="5.5" style="5" bestFit="1" customWidth="1"/>
     <col min="12" max="13" width="6" style="5" bestFit="1" customWidth="1"/>
     <col min="14" max="15" width="5.5" style="5" bestFit="1" customWidth="1"/>
@@ -829,11 +828,11 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="13" x14ac:dyDescent="0.15">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="38"/>
-      <c r="C3" s="34"/>
+      <c r="B3" s="36"/>
+      <c r="C3" s="32"/>
       <c r="D3" s="21"/>
       <c r="E3" s="16"/>
       <c r="F3" s="17"/>
@@ -863,10 +862,10 @@
         <v>1</v>
       </c>
       <c r="K4" s="1"/>
-      <c r="L4" s="23">
+      <c r="L4" s="22">
         <v>4</v>
       </c>
-      <c r="O4" s="24">
+      <c r="O4" s="23">
         <v>3</v>
       </c>
       <c r="U4" s="7">
@@ -880,7 +879,7 @@
       <c r="A5" s="1">
         <v>2</v>
       </c>
-      <c r="B5" s="28" t="s">
+      <c r="B5" s="27" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="1"/>
@@ -893,14 +892,14 @@
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
-      <c r="P5" s="29">
+      <c r="P5" s="28">
         <v>2</v>
       </c>
       <c r="Q5" s="1"/>
-      <c r="R5" s="30">
+      <c r="R5" s="29">
         <v>3</v>
       </c>
-      <c r="T5" s="30">
+      <c r="T5" s="29">
         <v>2</v>
       </c>
       <c r="W5" s="6">
@@ -926,7 +925,7 @@
       <c r="A7" s="1">
         <v>4</v>
       </c>
-      <c r="B7" s="28" t="s">
+      <c r="B7" s="27" t="s">
         <v>43</v>
       </c>
       <c r="C7" s="1"/>
@@ -947,15 +946,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="20" t="s">
+      <c r="B8" s="27" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="35" t="s">
+      <c r="C8" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D8" s="1">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E8" s="12" t="s">
         <v>4</v>
@@ -969,7 +968,10 @@
       <c r="M8" s="7">
         <v>4</v>
       </c>
-      <c r="P8" s="29">
+      <c r="P8" s="28">
+        <v>3</v>
+      </c>
+      <c r="Y8" s="19">
         <v>3</v>
       </c>
     </row>
@@ -977,10 +979,10 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="C9" s="35" t="s">
+      <c r="C9" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D9" s="1">
@@ -1005,7 +1007,7 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>1</v>
       </c>
       <c r="C10" s="1"/>
@@ -1030,18 +1032,18 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="35"/>
+      <c r="C11" s="33"/>
       <c r="D11" s="1">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="O11" s="24"/>
-      <c r="S11" s="32"/>
+      <c r="O11" s="37"/>
+      <c r="S11" s="37"/>
     </row>
     <row r="12" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
@@ -1074,7 +1076,7 @@
         <v>2</v>
       </c>
       <c r="F13" s="1"/>
-      <c r="L13" s="24">
+      <c r="L13" s="23">
         <v>1</v>
       </c>
       <c r="W13" s="6">
@@ -1085,7 +1087,7 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="27" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="1"/>
@@ -1093,15 +1095,15 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="E14" s="26"/>
-      <c r="F14" s="26"/>
-      <c r="G14" s="26"/>
-      <c r="H14" s="26"/>
-      <c r="I14" s="26"/>
-      <c r="J14" s="26"/>
-      <c r="K14" s="26"/>
-      <c r="L14" s="26"/>
-      <c r="Q14" s="26"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="Q14" s="25"/>
     </row>
     <row r="15" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15" s="1">
@@ -1140,27 +1142,27 @@
       <c r="U15" s="5"/>
       <c r="V15" s="5"/>
       <c r="W15" s="5"/>
-      <c r="X15" s="26"/>
-      <c r="Y15" s="26"/>
-      <c r="Z15" s="26"/>
-      <c r="AA15" s="26"/>
-      <c r="AB15" s="26"/>
-      <c r="AC15" s="26"/>
-      <c r="AD15" s="26"/>
-      <c r="AE15" s="26"/>
-      <c r="AF15" s="26"/>
-      <c r="AG15" s="26"/>
-      <c r="AH15" s="26"/>
-      <c r="AI15" s="26"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="25"/>
+      <c r="AI15" s="25"/>
     </row>
     <row r="16" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D16" s="1">
@@ -1176,29 +1178,29 @@
       <c r="J16" s="19">
         <v>4</v>
       </c>
-      <c r="M16" s="26"/>
-      <c r="N16" s="26"/>
-      <c r="O16" s="26"/>
-      <c r="P16" s="26"/>
-      <c r="R16" s="31">
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="R16" s="30">
         <v>2</v>
       </c>
-      <c r="S16" s="26"/>
-      <c r="T16" s="26"/>
-      <c r="U16" s="36">
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="34">
         <v>4</v>
       </c>
-      <c r="V16" s="26"/>
-      <c r="W16" s="26"/>
-    </row>
-    <row r="17" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+    </row>
+    <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>48</v>
       </c>
-      <c r="C17" s="35" t="s">
+      <c r="C17" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D17" s="1">
@@ -1209,21 +1211,21 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
       <c r="Q17" s="1"/>
-      <c r="R17" s="30">
+      <c r="R17" s="29">
         <v>1</v>
       </c>
-      <c r="S17" s="32">
+      <c r="S17" s="31">
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="C18" s="35" t="s">
+      <c r="C18" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D18" s="1">
@@ -1232,24 +1234,24 @@
       </c>
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
-      <c r="O18" s="24">
+      <c r="O18" s="23">
         <v>1</v>
       </c>
-      <c r="S18" s="32">
+      <c r="S18" s="31">
         <v>3</v>
       </c>
       <c r="X18" s="7">
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
       <c r="B19" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="35" t="s">
+      <c r="C19" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D19" s="1">
@@ -1268,11 +1270,11 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
-      <c r="B20" s="28" t="s">
+      <c r="B20" s="27" t="s">
         <v>49</v>
       </c>
       <c r="C20" s="1"/>
@@ -1285,11 +1287,11 @@
       <c r="G20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>10</v>
       </c>
       <c r="C21" s="1"/>
@@ -1304,18 +1306,18 @@
       <c r="K21" s="8">
         <v>1</v>
       </c>
-      <c r="T21" s="30">
+      <c r="T21" s="29">
         <v>1</v>
       </c>
       <c r="W21" s="6">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
-      <c r="B22" s="28" t="s">
+      <c r="B22" s="27" t="s">
         <v>50</v>
       </c>
       <c r="C22" s="1"/>
@@ -1330,14 +1332,14 @@
       <c r="U22" s="7">
         <v>3</v>
       </c>
-      <c r="V22" s="32">
+      <c r="V22" s="31">
         <v>2</v>
       </c>
       <c r="X22" s="7">
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1355,15 +1357,15 @@
       <c r="F23" s="11">
         <v>1</v>
       </c>
-      <c r="T23" s="30">
+      <c r="T23" s="29">
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="28" t="s">
+      <c r="B24" s="27" t="s">
         <v>53</v>
       </c>
       <c r="C24" s="1"/>
@@ -1376,11 +1378,11 @@
       <c r="G24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="28" t="s">
+      <c r="B25" s="27" t="s">
         <v>59</v>
       </c>
       <c r="C25" s="1"/>
@@ -1395,18 +1397,18 @@
       <c r="U25" s="7">
         <v>2</v>
       </c>
-      <c r="V25" s="32">
+      <c r="V25" s="31">
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C26" s="35" t="s">
+      <c r="C26" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D26" s="1">
@@ -1414,14 +1416,14 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="28" t="s">
+      <c r="B27" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="35" t="s">
+      <c r="C27" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D27" s="1">
@@ -1434,15 +1436,15 @@
       <c r="I27" s="8">
         <v>1</v>
       </c>
-      <c r="R27" s="30">
+      <c r="R27" s="29">
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="28" t="s">
+      <c r="B28" s="27" t="s">
         <v>52</v>
       </c>
       <c r="C28" s="1"/>
@@ -1456,11 +1458,11 @@
       <c r="L28" s="12"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="28" t="s">
+      <c r="B29" s="27" t="s">
         <v>55</v>
       </c>
       <c r="C29" s="1"/>
@@ -1473,45 +1475,48 @@
       <c r="G29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="28" t="s">
+      <c r="B30" s="27" t="s">
         <v>18</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M30" s="7">
         <v>3</v>
       </c>
-      <c r="O30" s="24">
+      <c r="O30" s="23">
         <v>4</v>
       </c>
-      <c r="P30" s="29">
+      <c r="P30" s="28">
         <v>1</v>
       </c>
-      <c r="S30" s="32">
+      <c r="S30" s="31">
         <v>2</v>
       </c>
-      <c r="V30" s="32">
+      <c r="V30" s="31">
         <v>3</v>
       </c>
-    </row>
-    <row r="31" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y30" s="19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="28" t="s">
+      <c r="B31" s="27" t="s">
         <v>26</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="12" t="s">
         <v>2</v>
@@ -1519,12 +1524,15 @@
       <c r="X31" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:24" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Y31" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="28" t="s">
+      <c r="B32" s="27" t="s">
         <v>45</v>
       </c>
       <c r="C32" s="1"/>
@@ -1544,62 +1552,56 @@
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="28" t="s">
+      <c r="B33" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="C33" s="35" t="s">
+      <c r="C33" s="33" t="s">
         <v>57</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="0"/>
+        <f>COUNTIF(F33:AI33,"&lt;&gt;")</f>
         <v>2</v>
       </c>
       <c r="E33" s="1"/>
       <c r="F33" s="1"/>
       <c r="G33" s="1"/>
       <c r="Q33" s="1"/>
-      <c r="S33" s="32">
+      <c r="S33" s="31">
         <v>1</v>
       </c>
-      <c r="T33" s="30">
+      <c r="T33" s="29">
         <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="35"/>
+      <c r="B34" s="27"/>
+      <c r="C34" s="33"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="Q34" s="1"/>
-      <c r="S34" s="39"/>
-      <c r="T34" s="39"/>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="35"/>
+      <c r="B35" s="27"/>
+      <c r="C35" s="33"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
       <c r="F35" s="1"/>
       <c r="G35" s="1"/>
       <c r="Q35" s="1"/>
-      <c r="S35" s="39"/>
-      <c r="T35" s="39"/>
     </row>
     <row r="36" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="1"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="35"/>
+      <c r="B36" s="27"/>
+      <c r="C36" s="33"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1"/>
       <c r="G36" s="1"/>
       <c r="Q36" s="1"/>
-      <c r="S36" s="39"/>
-      <c r="T36" s="39"/>
     </row>
     <row r="37" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="1"/>
@@ -1611,10 +1613,10 @@
       </c>
     </row>
     <row r="38" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="37" t="s">
+      <c r="A38" s="35" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="38"/>
+      <c r="B38" s="36"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <f>COUNTIF(F38:'song list'!END,"&lt;&gt;")</f>
@@ -1630,7 +1632,7 @@
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
-        <f>COUNTIF(F39:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F39:AI39,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1643,7 +1645,7 @@
       <c r="N39" s="19">
         <v>5</v>
       </c>
-      <c r="P39" s="29">
+      <c r="P39" s="28">
         <v>5</v>
       </c>
     </row>
@@ -1651,75 +1653,76 @@
       <c r="A40" s="1">
         <v>2</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>23</v>
+      <c r="B40" s="27" t="s">
+        <v>62</v>
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
-        <f>COUNTIF(F40:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E40" s="1"/>
+        <f>COUNTIF(F40:AI40,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>63</v>
+      </c>
       <c r="F40" s="1"/>
+      <c r="I40" s="37"/>
+      <c r="Y40" s="19">
+        <v>1</v>
+      </c>
       <c r="AB40" s="12"/>
     </row>
     <row r="41" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A41" s="1">
         <v>3</v>
       </c>
-      <c r="B41" s="20" t="s">
-        <v>30</v>
+      <c r="B41" s="2" t="s">
+        <v>23</v>
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
-        <f>COUNTIF(F41:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <f>COUNTIF(F41:AI41,"&lt;&gt;")</f>
+        <v>0</v>
       </c>
       <c r="E41" s="1"/>
       <c r="F41" s="1"/>
-      <c r="H41" s="6">
-        <v>5</v>
-      </c>
-      <c r="O41" s="24">
-        <v>2</v>
-      </c>
     </row>
     <row r="42" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A42" s="1">
         <v>4</v>
       </c>
-      <c r="B42" s="28" t="s">
-        <v>47</v>
+      <c r="B42" s="20" t="s">
+        <v>30</v>
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
-        <f>COUNTIF(F42:'song list'!END,"&lt;&gt;")</f>
-        <v>1</v>
+        <f>COUNTIF(F42:AI42,"&lt;&gt;")</f>
+        <v>2</v>
       </c>
       <c r="E42" s="1"/>
       <c r="F42" s="1"/>
-      <c r="M42" s="7">
+      <c r="H42" s="6">
         <v>5</v>
+      </c>
+      <c r="O42" s="23">
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A43" s="1">
         <v>5</v>
       </c>
-      <c r="B43" s="20" t="s">
-        <v>12</v>
+      <c r="B43" s="27" t="s">
+        <v>47</v>
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
-        <f>COUNTIF(F43:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F43:AI43,"&lt;&gt;")</f>
         <v>1</v>
       </c>
-      <c r="E43" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="E43" s="1"/>
       <c r="F43" s="1"/>
-      <c r="I43" s="8">
-        <v>3</v>
+      <c r="M43" s="7">
+        <v>5</v>
       </c>
     </row>
     <row r="44" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -1727,353 +1730,365 @@
         <v>6</v>
       </c>
       <c r="B44" s="20" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
-        <f>COUNTIF(F44:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
+        <f>COUNTIF(F44:AI44,"&lt;&gt;")</f>
+        <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F44" s="1"/>
       <c r="I44" s="8">
-        <v>5</v>
-      </c>
-      <c r="K44" s="8">
-        <v>4</v>
-      </c>
-      <c r="P44" s="29">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="1">
         <v>7</v>
       </c>
-      <c r="B45" s="28" t="s">
-        <v>51</v>
+      <c r="B45" s="20" t="s">
+        <v>40</v>
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
-        <f>COUNTIF(F45:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F45:AI45,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E45" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E45" s="26"/>
-      <c r="F45" s="26"/>
-      <c r="G45" s="26"/>
-      <c r="H45" s="26"/>
-      <c r="I45" s="26"/>
-      <c r="J45" s="26"/>
-      <c r="K45" s="26"/>
-      <c r="L45" s="26"/>
-      <c r="Q45" s="26"/>
-      <c r="V45" s="32">
-        <v>1</v>
-      </c>
-      <c r="W45" s="6">
+      <c r="F45" s="1"/>
+      <c r="I45" s="8">
         <v>5</v>
       </c>
-    </row>
-    <row r="46" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K45" s="8">
+        <v>4</v>
+      </c>
+      <c r="P45" s="28">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A46" s="1">
         <v>8</v>
       </c>
-      <c r="B46" s="20" t="s">
-        <v>22</v>
+      <c r="B46" s="27" t="s">
+        <v>61</v>
       </c>
       <c r="C46" s="1"/>
-      <c r="D46" s="1">
-        <f>COUNTIF(F46:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F46" s="10">
-        <v>5</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5"/>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
-      <c r="M46" s="26"/>
-      <c r="N46" s="27">
-        <v>3</v>
-      </c>
-      <c r="O46" s="26"/>
-      <c r="P46" s="26"/>
-      <c r="Q46" s="5"/>
-      <c r="R46" s="26"/>
-      <c r="S46" s="33">
-        <v>5</v>
-      </c>
-      <c r="T46" s="26"/>
-      <c r="U46" s="26"/>
-      <c r="V46" s="26"/>
-      <c r="W46" s="26"/>
-      <c r="X46" s="26"/>
-      <c r="Y46" s="26"/>
-      <c r="Z46" s="26"/>
-      <c r="AA46" s="26"/>
-      <c r="AB46" s="26"/>
-      <c r="AC46" s="26"/>
-      <c r="AD46" s="26"/>
-      <c r="AE46" s="26"/>
-      <c r="AF46" s="26"/>
-      <c r="AG46" s="26"/>
-      <c r="AH46" s="26"/>
-      <c r="AI46" s="26"/>
-    </row>
-    <row r="47" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="D46" s="1"/>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+    <row r="47" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
         <v>9</v>
       </c>
-      <c r="B47" s="28" t="s">
-        <v>6</v>
+      <c r="B47" s="27" t="s">
+        <v>51</v>
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
-        <f>COUNTIF(F47:'song list'!END,"&lt;&gt;")</f>
-        <v>3</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F47" s="10">
+        <f>COUNTIF(F47:AI47,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="L47" s="24">
+      <c r="E47" s="25"/>
+      <c r="F47" s="25"/>
+      <c r="G47" s="25"/>
+      <c r="H47" s="25"/>
+      <c r="I47" s="25"/>
+      <c r="J47" s="25"/>
+      <c r="K47" s="25"/>
+      <c r="L47" s="25"/>
+      <c r="M47" s="5"/>
+      <c r="N47" s="5"/>
+      <c r="O47" s="5"/>
+      <c r="P47" s="5"/>
+      <c r="Q47" s="25"/>
+      <c r="R47" s="5"/>
+      <c r="S47" s="5"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="5"/>
+      <c r="V47" s="31">
+        <v>1</v>
+      </c>
+      <c r="W47" s="6">
         <v>5</v>
       </c>
-      <c r="R47" s="30">
-        <v>5</v>
-      </c>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="25"/>
+      <c r="Z47" s="25"/>
+      <c r="AA47" s="25"/>
+      <c r="AB47" s="25"/>
+      <c r="AC47" s="25"/>
+      <c r="AD47" s="25"/>
+      <c r="AE47" s="25"/>
+      <c r="AF47" s="25"/>
+      <c r="AG47" s="25"/>
+      <c r="AH47" s="25"/>
+      <c r="AI47" s="25"/>
     </row>
     <row r="48" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A48" s="1">
         <v>10</v>
       </c>
       <c r="B48" s="20" t="s">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
-        <f>COUNTIF(F48:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F48:AI48,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E48" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="H48" s="6">
-        <v>4</v>
-      </c>
-      <c r="L48" s="24">
+      <c r="F48" s="10">
+        <v>5</v>
+      </c>
+      <c r="M48" s="25"/>
+      <c r="N48" s="26">
         <v>3</v>
       </c>
-    </row>
-    <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="O48" s="25"/>
+      <c r="P48" s="25"/>
+      <c r="R48" s="25"/>
+      <c r="S48" s="38">
+        <v>5</v>
+      </c>
+      <c r="T48" s="25"/>
+      <c r="U48" s="25"/>
+      <c r="V48" s="25"/>
+      <c r="W48" s="25"/>
+      <c r="X48" s="25"/>
+    </row>
+    <row r="49" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>11</v>
       </c>
-      <c r="B49" s="20" t="s">
-        <v>5</v>
+      <c r="B49" s="27" t="s">
+        <v>6</v>
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
-        <f>COUNTIF(F49:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F49:AI49,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F49" s="10">
         <v>2</v>
       </c>
-      <c r="F49" s="1"/>
-      <c r="G49" s="7">
+      <c r="L49" s="23">
         <v>5</v>
       </c>
-      <c r="K49" s="8">
+      <c r="R49" s="29">
         <v>5</v>
       </c>
-      <c r="Q49" s="7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="50" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>12</v>
       </c>
       <c r="B50" s="20" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
-        <f>COUNTIF(F50:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F50:AI50,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E50" s="1" t="s">
-        <v>2</v>
-      </c>
+      <c r="E50" s="1"/>
       <c r="F50" s="1"/>
-      <c r="J50" s="19">
+      <c r="H50" s="6">
+        <v>4</v>
+      </c>
+      <c r="L50" s="23">
         <v>3</v>
       </c>
-      <c r="K50" s="8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="51" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>13</v>
       </c>
       <c r="B51" s="20" t="s">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
-        <f>COUNTIF(F51:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F51:AI51,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E51" s="1"/>
       <c r="F51" s="1"/>
-      <c r="H51" s="6">
-        <v>2</v>
-      </c>
-      <c r="M51" s="7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G51" s="7">
+        <v>5</v>
+      </c>
+      <c r="K51" s="8">
+        <v>5</v>
+      </c>
+      <c r="Q51" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>14</v>
       </c>
       <c r="B52" s="20" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
-        <f>COUNTIF(F52:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F52:AI52,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
+      <c r="E52" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F52" s="1"/>
+      <c r="J52" s="19">
         <v>3</v>
       </c>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="7">
-        <v>1</v>
-      </c>
-      <c r="L52" s="23">
-        <v>2</v>
-      </c>
-      <c r="Q52" s="7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K52" s="8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>15</v>
       </c>
-      <c r="B53" s="22" t="s">
-        <v>25</v>
+      <c r="B53" s="20" t="s">
+        <v>19</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
-        <f>COUNTIF(F53:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F53:AI53,"&lt;&gt;")</f>
         <v>2</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="H53" s="6">
         <v>2</v>
       </c>
-      <c r="F53" s="1"/>
-      <c r="K53" s="8">
+      <c r="M53" s="7">
         <v>2</v>
       </c>
-      <c r="L53" s="25"/>
-      <c r="O53" s="24">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="54" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    </row>
+    <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>16</v>
       </c>
-      <c r="B54" s="28" t="s">
-        <v>56</v>
+      <c r="B54" s="20" t="s">
+        <v>21</v>
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
-        <f>COUNTIF(F54:'song list'!END,"&lt;&gt;")</f>
-        <v>2</v>
+        <f>COUNTIF(F54:AI54,"&lt;&gt;")</f>
+        <v>3</v>
       </c>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
-      <c r="J54" s="19"/>
-      <c r="K54" s="8"/>
-      <c r="T54" s="30">
-        <v>5</v>
-      </c>
-      <c r="V54" s="32">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="G54" s="7">
+        <v>1</v>
+      </c>
+      <c r="L54" s="22">
+        <v>2</v>
+      </c>
+      <c r="Q54" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>17</v>
       </c>
-      <c r="B55" s="28" t="s">
-        <v>24</v>
+      <c r="B55" s="27" t="s">
+        <v>25</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
-        <f>COUNTIF(F55:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E55" s="1"/>
+        <f>COUNTIF(F55:AI55,"&lt;&gt;")</f>
+        <v>3</v>
+      </c>
+      <c r="E55" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F55" s="1"/>
-    </row>
-    <row r="56" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="K55" s="8">
+        <v>2</v>
+      </c>
+      <c r="L55" s="24"/>
+      <c r="O55" s="23">
+        <v>5</v>
+      </c>
+      <c r="Y55" s="19">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>18</v>
       </c>
-      <c r="B56" s="28" t="s">
-        <v>61</v>
+      <c r="B56" s="27" t="s">
+        <v>56</v>
       </c>
       <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
+      <c r="D56" s="1">
+        <f>COUNTIF(F56:AI56,"&lt;&gt;")</f>
+        <v>2</v>
+      </c>
       <c r="E56" s="1"/>
       <c r="F56" s="1"/>
-    </row>
-    <row r="57" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="1"/>
-      <c r="B57" s="28"/>
+      <c r="J56" s="19"/>
+      <c r="K56" s="8"/>
+      <c r="T56" s="29">
+        <v>5</v>
+      </c>
+      <c r="V56" s="31">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A57" s="1">
+        <v>19</v>
+      </c>
+      <c r="B57" s="27" t="s">
+        <v>24</v>
+      </c>
       <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
+      <c r="D57" s="1">
+        <f>COUNTIF(F57:AI57,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1"/>
-      <c r="B58" s="28"/>
+      <c r="B58" s="27"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1"/>
-      <c r="B59" s="4"/>
+      <c r="B59" s="27"/>
       <c r="C59" s="1"/>
-      <c r="D59" s="1">
-        <f>COUNTIF(F59:'song list'!END,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
+      <c r="D59" s="1"/>
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="37" t="s">
-        <v>36</v>
-      </c>
-      <c r="B60" s="38"/>
+    <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A60" s="1"/>
+      <c r="B60" s="4"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1">
         <f>COUNTIF(F60:'song list'!END,"&lt;&gt;")</f>
@@ -2082,51 +2097,59 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="1">
-        <v>1</v>
-      </c>
-      <c r="B61" s="20" t="s">
-        <v>31</v>
-      </c>
+    <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="B61" s="36"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
         <f>COUNTIF(F61:'song list'!END,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+    </row>
+    <row r="62" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A62" s="1">
         <v>1</v>
       </c>
-      <c r="E61" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="F61" s="1"/>
-      <c r="I61" s="8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="1">
-        <v>2</v>
-      </c>
       <c r="B62" s="20" t="s">
-        <v>38</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C62" s="1"/>
       <c r="D62" s="1">
-        <f>COUNTIF(F62:'song list'!END,"&lt;&gt;")</f>
+        <f>COUNTIF(F62:AI62,"&lt;&gt;")</f>
         <v>1</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>2</v>
       </c>
       <c r="F62" s="1"/>
-      <c r="J62" s="19">
+      <c r="I62" s="8">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="1"/>
-      <c r="E63" s="1"/>
+    <row r="63" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A63" s="1">
+        <v>2</v>
+      </c>
+      <c r="B63" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="D63" s="1">
+        <f>COUNTIF(F63:AI63,"&lt;&gt;")</f>
+        <v>1</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>2</v>
+      </c>
       <c r="F63" s="1"/>
-    </row>
-    <row r="64" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="J63" s="19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -2366,7 +2389,7 @@
       <c r="E111" s="1"/>
       <c r="F111" s="1"/>
     </row>
-    <row r="112" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+    <row r="112" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A112" s="1"/>
       <c r="E112" s="1"/>
       <c r="F112" s="1"/>
@@ -6941,39 +6964,44 @@
       <c r="E1026" s="1"/>
       <c r="F1026" s="1"/>
     </row>
+    <row r="1027" spans="1:6" ht="13" x14ac:dyDescent="0.15">
+      <c r="A1027" s="1"/>
+      <c r="E1027" s="1"/>
+      <c r="F1027" s="1"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B4:W33">
-    <sortCondition ref="B4:B33"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B39:X57">
+    <sortCondition ref="B39:B57"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A61:B61"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="B14" r:id="rId1" xr:uid="{CDC70FF9-28EC-5141-BB34-567453BC7B65}"/>
     <hyperlink ref="B30" r:id="rId2" xr:uid="{8C7F6EDC-9D4C-7645-A18D-457BA77361D3}"/>
     <hyperlink ref="B32" r:id="rId3" xr:uid="{C198F295-95F1-E042-8452-0DA39E40F1FF}"/>
-    <hyperlink ref="B42" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
-    <hyperlink ref="B55" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
+    <hyperlink ref="B43" r:id="rId4" xr:uid="{A4107288-6FF5-1D41-AF33-89BF1BB8BC75}"/>
+    <hyperlink ref="B57" r:id="rId5" xr:uid="{A1C76E2C-93E9-6B43-B0E3-ECA867246606}"/>
     <hyperlink ref="B17" r:id="rId6" xr:uid="{C73B5BF2-2C3C-BB48-86C6-2BB15F4B391A}"/>
     <hyperlink ref="B20" r:id="rId7" xr:uid="{2FDCD454-AE6F-7F46-88F5-1ED53DAB6DB3}"/>
     <hyperlink ref="B22" r:id="rId8" xr:uid="{72FA4902-65C8-4E4A-876B-4F0427703577}"/>
-    <hyperlink ref="B45" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
+    <hyperlink ref="B47" r:id="rId9" xr:uid="{7A951EB9-3C1D-4344-A7AD-FB1AC9B6AE70}"/>
     <hyperlink ref="B28" r:id="rId10" xr:uid="{160125C2-37BC-7C44-9B7E-5465CC162A13}"/>
     <hyperlink ref="B7" r:id="rId11" xr:uid="{FF27C7C7-7471-A54C-835D-7E6FF4EB2FE2}"/>
     <hyperlink ref="B26" r:id="rId12" xr:uid="{2DDD30D8-23B9-0140-8427-F2DAEB4C0F8D}"/>
     <hyperlink ref="B5" r:id="rId13" xr:uid="{B12731C3-69A2-A04D-B04F-1E2883D09F23}"/>
     <hyperlink ref="B27" r:id="rId14" xr:uid="{7334FFF6-184A-EE44-82BD-0A44CDAF10A0}"/>
     <hyperlink ref="B16" r:id="rId15" xr:uid="{578651F0-DCCC-804E-9EB4-119A367F8422}"/>
-    <hyperlink ref="B47" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
+    <hyperlink ref="B49" r:id="rId16" xr:uid="{AFB4C929-1446-294B-A6E3-D9AD847B9BC7}"/>
     <hyperlink ref="B33" r:id="rId17" xr:uid="{AE2BF267-73E2-3E49-9BD9-DB68D2F21F78}"/>
     <hyperlink ref="B9" r:id="rId18" xr:uid="{35808B54-3BA0-4E4F-98BE-BF698C7ED026}"/>
     <hyperlink ref="B10" r:id="rId19" xr:uid="{3451B5BF-E449-724C-9A39-7BC984CED4FC}"/>
     <hyperlink ref="B29" r:id="rId20" xr:uid="{6B1DEF0D-81B4-BA42-A66D-70126B2B7E9E}"/>
     <hyperlink ref="B18" r:id="rId21" xr:uid="{13A72618-DFD5-1541-BC0F-C05614EA627B}"/>
     <hyperlink ref="B24" r:id="rId22" xr:uid="{0299DF70-E4BD-AF4C-8FD5-04F6F8E35DFF}"/>
-    <hyperlink ref="B54" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
+    <hyperlink ref="B56" r:id="rId23" xr:uid="{667C311E-8605-E042-9754-8633355F13BD}"/>
     <hyperlink ref="B21" r:id="rId24" xr:uid="{DBA4484E-9180-3C49-A6CD-EB3EDBBF1475}"/>
     <hyperlink ref="C9" r:id="rId25" xr:uid="{93134F2E-198C-D74C-8193-8EFB343FFEA8}"/>
     <hyperlink ref="C27" r:id="rId26" xr:uid="{53F603D0-6CF7-C644-8BCC-AB0986CF1653}"/>
@@ -6986,6 +7014,9 @@
     <hyperlink ref="C33" r:id="rId33" xr:uid="{9E881A86-1611-FE46-82E2-9CC134F32162}"/>
     <hyperlink ref="B11" r:id="rId34" xr:uid="{646C8938-F9C4-8349-9383-8BF3C536D75D}"/>
     <hyperlink ref="B31" r:id="rId35" xr:uid="{B242CBB2-6F0F-B946-B48D-BB7DF3D3B30E}"/>
+    <hyperlink ref="B40" r:id="rId36" xr:uid="{59800823-2BE3-B940-B210-EBE78C748231}"/>
+    <hyperlink ref="B8" r:id="rId37" xr:uid="{EC988224-A529-584A-B115-B56E682A3BDC}"/>
+    <hyperlink ref="B55" r:id="rId38" xr:uid="{B339014F-FE73-644E-9DC3-A8FEB98D5F64}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2DBCE9E-215A-2447-A502-1AA9950D0F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28DBE6-EA3B-6F43-A20E-B0D89174AAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3860" yWindow="600" windowWidth="16500" windowHeight="26140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17080" yWindow="-3960" windowWidth="16640" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -295,7 +295,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -362,6 +362,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -376,7 +382,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -470,16 +476,22 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -828,10 +840,10 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="13" x14ac:dyDescent="0.15">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="36" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="36"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="32"/>
       <c r="D3" s="21"/>
       <c r="E3" s="16"/>
@@ -915,7 +927,7 @@
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D33" si="0">COUNTIF(F6:AI6,"&lt;&gt;")</f>
+        <f t="shared" ref="D6:D32" si="0">COUNTIF(F6:AI6,"&lt;&gt;")</f>
         <v>0</v>
       </c>
       <c r="E6" s="1"/>
@@ -1042,8 +1054,6 @@
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
-      <c r="O11" s="37"/>
-      <c r="S11" s="37"/>
     </row>
     <row r="12" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" s="1">
@@ -1193,7 +1203,7 @@
       <c r="V16" s="25"/>
       <c r="W16" s="25"/>
     </row>
-    <row r="17" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1205,7 +1215,7 @@
       </c>
       <c r="D17" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
@@ -1217,8 +1227,11 @@
       <c r="S17" s="31">
         <v>4</v>
       </c>
-    </row>
-    <row r="18" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Z17" s="38">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1244,11 +1257,11 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="20" t="s">
+      <c r="B19" s="27" t="s">
         <v>20</v>
       </c>
       <c r="C19" s="33" t="s">
@@ -1256,7 +1269,7 @@
       </c>
       <c r="D19" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
@@ -1269,8 +1282,11 @@
       <c r="Q19" s="9">
         <v>4</v>
       </c>
-    </row>
-    <row r="20" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Z19" s="38">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1287,7 +1303,7 @@
       <c r="G20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1313,7 +1329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1339,7 +1355,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1361,7 +1377,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="24" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1378,7 +1394,7 @@
       <c r="G24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1401,7 +1417,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1416,7 +1432,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1440,7 +1456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1458,7 +1474,7 @@
       <c r="L28" s="12"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1475,7 +1491,7 @@
       <c r="G29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1506,7 +1522,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1527,8 +1543,9 @@
       <c r="Y31" s="19">
         <v>2</v>
       </c>
-    </row>
-    <row r="32" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Z31" s="39"/>
+    </row>
+    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1538,13 +1555,16 @@
       <c r="C32" s="1"/>
       <c r="D32" s="1">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F32" s="1"/>
       <c r="X32" s="7">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="38">
         <v>1</v>
       </c>
     </row>
@@ -1613,10 +1633,10 @@
       </c>
     </row>
     <row r="38" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="35" t="s">
+      <c r="A38" s="36" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="36"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <f>COUNTIF(F38:'song list'!END,"&lt;&gt;")</f>
@@ -1632,7 +1652,7 @@
       </c>
       <c r="C39" s="1"/>
       <c r="D39" s="1">
-        <f>COUNTIF(F39:AI39,"&lt;&gt;")</f>
+        <f t="shared" ref="D39:D45" si="1">COUNTIF(F39:AI39,"&lt;&gt;")</f>
         <v>3</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -1658,14 +1678,13 @@
       </c>
       <c r="C40" s="1"/>
       <c r="D40" s="1">
-        <f>COUNTIF(F40:AI40,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E40" s="1" t="s">
         <v>63</v>
       </c>
       <c r="F40" s="1"/>
-      <c r="I40" s="37"/>
       <c r="Y40" s="19">
         <v>1</v>
       </c>
@@ -1680,7 +1699,7 @@
       </c>
       <c r="C41" s="1"/>
       <c r="D41" s="1">
-        <f>COUNTIF(F41:AI41,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E41" s="1"/>
@@ -1695,7 +1714,7 @@
       </c>
       <c r="C42" s="1"/>
       <c r="D42" s="1">
-        <f>COUNTIF(F42:AI42,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>2</v>
       </c>
       <c r="E42" s="1"/>
@@ -1716,7 +1735,7 @@
       </c>
       <c r="C43" s="1"/>
       <c r="D43" s="1">
-        <f>COUNTIF(F43:AI43,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E43" s="1"/>
@@ -1734,7 +1753,7 @@
       </c>
       <c r="C44" s="1"/>
       <c r="D44" s="1">
-        <f>COUNTIF(F44:AI44,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>1</v>
       </c>
       <c r="E44" s="1" t="s">
@@ -1754,7 +1773,7 @@
       </c>
       <c r="C45" s="1"/>
       <c r="D45" s="1">
-        <f>COUNTIF(F45:AI45,"&lt;&gt;")</f>
+        <f t="shared" si="1"/>
         <v>3</v>
       </c>
       <c r="E45" s="1" t="s">
@@ -1792,8 +1811,8 @@
       </c>
       <c r="C47" s="1"/>
       <c r="D47" s="1">
-        <f>COUNTIF(F47:AI47,"&lt;&gt;")</f>
-        <v>2</v>
+        <f t="shared" ref="D47:D57" si="2">COUNTIF(F47:AI47,"&lt;&gt;")</f>
+        <v>3</v>
       </c>
       <c r="E47" s="25"/>
       <c r="F47" s="25"/>
@@ -1820,7 +1839,9 @@
       </c>
       <c r="X47" s="5"/>
       <c r="Y47" s="25"/>
-      <c r="Z47" s="25"/>
+      <c r="Z47" s="40">
+        <v>5</v>
+      </c>
       <c r="AA47" s="25"/>
       <c r="AB47" s="25"/>
       <c r="AC47" s="25"/>
@@ -1840,7 +1861,7 @@
       </c>
       <c r="C48" s="1"/>
       <c r="D48" s="1">
-        <f>COUNTIF(F48:AI48,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="E48" s="1" t="s">
@@ -1856,7 +1877,7 @@
       <c r="O48" s="25"/>
       <c r="P48" s="25"/>
       <c r="R48" s="25"/>
-      <c r="S48" s="38">
+      <c r="S48" s="35">
         <v>5</v>
       </c>
       <c r="T48" s="25"/>
@@ -1865,7 +1886,7 @@
       <c r="W48" s="25"/>
       <c r="X48" s="25"/>
     </row>
-    <row r="49" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A49" s="1">
         <v>11</v>
       </c>
@@ -1874,7 +1895,7 @@
       </c>
       <c r="C49" s="1"/>
       <c r="D49" s="1">
-        <f>COUNTIF(F49:AI49,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="E49" s="1" t="s">
@@ -1890,7 +1911,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A50" s="1">
         <v>12</v>
       </c>
@@ -1899,7 +1920,7 @@
       </c>
       <c r="C50" s="1"/>
       <c r="D50" s="1">
-        <f>COUNTIF(F50:AI50,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E50" s="1"/>
@@ -1911,7 +1932,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="51" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A51" s="1">
         <v>13</v>
       </c>
@@ -1920,7 +1941,7 @@
       </c>
       <c r="C51" s="1"/>
       <c r="D51" s="1">
-        <f>COUNTIF(F51:AI51,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="E51" s="1" t="s">
@@ -1937,7 +1958,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="1">
         <v>14</v>
       </c>
@@ -1946,7 +1967,7 @@
       </c>
       <c r="C52" s="1"/>
       <c r="D52" s="1">
-        <f>COUNTIF(F52:AI52,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E52" s="1" t="s">
@@ -1960,17 +1981,17 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A53" s="1">
         <v>15</v>
       </c>
-      <c r="B53" s="20" t="s">
+      <c r="B53" s="27" t="s">
         <v>19</v>
       </c>
       <c r="C53" s="1"/>
       <c r="D53" s="1">
-        <f>COUNTIF(F53:AI53,"&lt;&gt;")</f>
-        <v>2</v>
+        <f t="shared" si="2"/>
+        <v>3</v>
       </c>
       <c r="E53" s="1"/>
       <c r="F53" s="1"/>
@@ -1980,8 +2001,11 @@
       <c r="M53" s="7">
         <v>2</v>
       </c>
-    </row>
-    <row r="54" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="Z53" s="38">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A54" s="1">
         <v>16</v>
       </c>
@@ -1990,7 +2014,7 @@
       </c>
       <c r="C54" s="1"/>
       <c r="D54" s="1">
-        <f>COUNTIF(F54:AI54,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="E54" s="1"/>
@@ -2005,7 +2029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="55" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A55" s="1">
         <v>17</v>
       </c>
@@ -2014,7 +2038,7 @@
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1">
-        <f>COUNTIF(F55:AI55,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="E55" s="1" t="s">
@@ -2032,7 +2056,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="56" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A56" s="1">
         <v>18</v>
       </c>
@@ -2041,7 +2065,7 @@
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1">
-        <f>COUNTIF(F56:AI56,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="E56" s="1"/>
@@ -2055,7 +2079,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="57" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A57" s="1">
         <v>19</v>
       </c>
@@ -2064,13 +2088,13 @@
       </c>
       <c r="C57" s="1"/>
       <c r="D57" s="1">
-        <f>COUNTIF(F57:AI57,"&lt;&gt;")</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E57" s="1"/>
       <c r="F57" s="1"/>
     </row>
-    <row r="58" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A58" s="1"/>
       <c r="B58" s="27"/>
       <c r="C58" s="1"/>
@@ -2078,7 +2102,7 @@
       <c r="E58" s="1"/>
       <c r="F58" s="1"/>
     </row>
-    <row r="59" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A59" s="1"/>
       <c r="B59" s="27"/>
       <c r="C59" s="1"/>
@@ -2086,7 +2110,7 @@
       <c r="E59" s="1"/>
       <c r="F59" s="1"/>
     </row>
-    <row r="60" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A60" s="1"/>
       <c r="B60" s="4"/>
       <c r="C60" s="1"/>
@@ -2097,11 +2121,11 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
     </row>
-    <row r="61" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="35" t="s">
+    <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="A61" s="36" t="s">
         <v>36</v>
       </c>
-      <c r="B61" s="36"/>
+      <c r="B61" s="37"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
         <f>COUNTIF(F61:'song list'!END,"&lt;&gt;")</f>
@@ -2110,7 +2134,7 @@
       <c r="E61" s="1"/>
       <c r="F61" s="1"/>
     </row>
-    <row r="62" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A62" s="1">
         <v>1</v>
       </c>
@@ -2130,7 +2154,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A63" s="1">
         <v>2</v>
       </c>
@@ -2149,7 +2173,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A64" s="1"/>
       <c r="E64" s="1"/>
       <c r="F64" s="1"/>
@@ -7017,6 +7041,8 @@
     <hyperlink ref="B40" r:id="rId36" xr:uid="{59800823-2BE3-B940-B210-EBE78C748231}"/>
     <hyperlink ref="B8" r:id="rId37" xr:uid="{EC988224-A529-584A-B115-B56E682A3BDC}"/>
     <hyperlink ref="B55" r:id="rId38" xr:uid="{B339014F-FE73-644E-9DC3-A8FEB98D5F64}"/>
+    <hyperlink ref="B53" r:id="rId39" xr:uid="{E9872149-A9DB-264E-90DF-27490F0A05E9}"/>
+    <hyperlink ref="B19" r:id="rId40" xr:uid="{B11CC4F6-040A-9441-A79D-83752EB074AE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC28DBE6-EA3B-6F43-A20E-B0D89174AAD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2691BE59-CDE3-AD45-B73F-456C3CC69474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17080" yWindow="-3960" windowWidth="16640" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23560" yWindow="-3960" windowWidth="23120" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
   <si>
     <t>Key</t>
   </si>
@@ -229,6 +229,9 @@
   <si>
     <t>C,D</t>
   </si>
+  <si>
+    <t>Yet Not I but through Christ in me</t>
+  </si>
 </sst>
 </file>
 
@@ -382,7 +385,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -479,20 +482,17 @@
     <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -840,10 +840,10 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="13" x14ac:dyDescent="0.15">
-      <c r="A3" s="36" t="s">
+      <c r="A3" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="37"/>
+      <c r="B3" s="39"/>
       <c r="C3" s="32"/>
       <c r="D3" s="21"/>
       <c r="E3" s="16"/>
@@ -1227,7 +1227,7 @@
       <c r="S17" s="31">
         <v>4</v>
       </c>
-      <c r="Z17" s="38">
+      <c r="Z17" s="36">
         <v>2</v>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       <c r="Q19" s="9">
         <v>4</v>
       </c>
-      <c r="Z19" s="38">
+      <c r="Z19" s="36">
         <v>4</v>
       </c>
     </row>
@@ -1543,7 +1543,6 @@
       <c r="Y31" s="19">
         <v>2</v>
       </c>
-      <c r="Z31" s="39"/>
     </row>
     <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
@@ -1564,7 +1563,7 @@
       <c r="X32" s="7">
         <v>1</v>
       </c>
-      <c r="Z32" s="38">
+      <c r="Z32" s="36">
         <v>1</v>
       </c>
     </row>
@@ -1594,10 +1593,17 @@
       </c>
     </row>
     <row r="34" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="1"/>
-      <c r="B34" s="27"/>
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="27" t="s">
+        <v>64</v>
+      </c>
       <c r="C34" s="33"/>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1">
+        <f>COUNTIF(F34:AI34,"&lt;&gt;")</f>
+        <v>0</v>
+      </c>
       <c r="E34" s="1"/>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
@@ -1633,10 +1639,10 @@
       </c>
     </row>
     <row r="38" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="36" t="s">
+      <c r="A38" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="37"/>
+      <c r="B38" s="39"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <f>COUNTIF(F38:'song list'!END,"&lt;&gt;")</f>
@@ -1839,7 +1845,7 @@
       </c>
       <c r="X47" s="5"/>
       <c r="Y47" s="25"/>
-      <c r="Z47" s="40">
+      <c r="Z47" s="37">
         <v>5</v>
       </c>
       <c r="AA47" s="25"/>
@@ -2001,7 +2007,7 @@
       <c r="M53" s="7">
         <v>2</v>
       </c>
-      <c r="Z53" s="38">
+      <c r="Z53" s="36">
         <v>3</v>
       </c>
     </row>
@@ -2122,10 +2128,10 @@
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="36" t="s">
+      <c r="A61" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="B61" s="37"/>
+      <c r="B61" s="39"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
         <f>COUNTIF(F61:'song list'!END,"&lt;&gt;")</f>
@@ -7043,6 +7049,7 @@
     <hyperlink ref="B55" r:id="rId38" xr:uid="{B339014F-FE73-644E-9DC3-A8FEB98D5F64}"/>
     <hyperlink ref="B53" r:id="rId39" xr:uid="{E9872149-A9DB-264E-90DF-27490F0A05E9}"/>
     <hyperlink ref="B19" r:id="rId40" xr:uid="{B11CC4F6-040A-9441-A79D-83752EB074AE}"/>
+    <hyperlink ref="B34" r:id="rId41" xr:uid="{B49926D5-FED1-B44A-B7BB-C47CB538FFD7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2691BE59-CDE3-AD45-B73F-456C3CC69474}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1483344-0C37-AF41-A7BE-5E112D82C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-23560" yWindow="-3960" windowWidth="23120" windowHeight="20460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4540" yWindow="660" windowWidth="18220" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="65">
   <si>
     <t>Key</t>
   </si>
@@ -298,7 +298,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -371,6 +371,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -385,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -493,6 +499,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1203,7 +1212,7 @@
       <c r="V16" s="25"/>
       <c r="W16" s="25"/>
     </row>
-    <row r="17" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="17" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="1">
         <v>15</v>
       </c>
@@ -1231,7 +1240,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="18" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="1">
         <v>16</v>
       </c>
@@ -1257,7 +1266,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="19" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="19" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="1">
         <v>17</v>
       </c>
@@ -1286,7 +1295,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="20" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1303,7 +1312,7 @@
       <c r="G20" s="1"/>
       <c r="Q20" s="1"/>
     </row>
-    <row r="21" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="21" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1">
         <v>19</v>
       </c>
@@ -1313,7 +1322,7 @@
       <c r="C21" s="1"/>
       <c r="D21" s="1">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>2</v>
@@ -1328,8 +1337,11 @@
       <c r="W21" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA21" s="40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A22" s="1">
         <v>20</v>
       </c>
@@ -1355,7 +1367,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="23" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="1">
         <v>21</v>
       </c>
@@ -1365,7 +1377,7 @@
       <c r="C23" s="1"/>
       <c r="D23" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>4</v>
@@ -1376,8 +1388,11 @@
       <c r="T23" s="29">
         <v>3</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA23" s="40">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A24" s="1">
         <v>22</v>
       </c>
@@ -1394,7 +1409,7 @@
       <c r="G24" s="1"/>
       <c r="Q24" s="1"/>
     </row>
-    <row r="25" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="25" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -1404,7 +1419,7 @@
       <c r="C25" s="1"/>
       <c r="D25" s="1">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -1416,8 +1431,11 @@
       <c r="V25" s="31">
         <v>4</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="AA25" s="40">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="1">
         <v>24</v>
       </c>
@@ -1432,7 +1450,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="27" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="1">
         <v>25</v>
       </c>
@@ -1456,7 +1474,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="28" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="1">
         <v>26</v>
       </c>
@@ -1474,7 +1492,7 @@
       <c r="L28" s="12"/>
       <c r="Q28" s="1"/>
     </row>
-    <row r="29" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="29" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -1491,7 +1509,7 @@
       <c r="G29" s="1"/>
       <c r="Q29" s="1"/>
     </row>
-    <row r="30" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -1522,7 +1540,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -1544,7 +1562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -1602,12 +1620,17 @@
       <c r="C34" s="33"/>
       <c r="D34" s="1">
         <f>COUNTIF(F34:AI34,"&lt;&gt;")</f>
-        <v>0</v>
-      </c>
-      <c r="E34" s="1"/>
+        <v>1</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>4</v>
+      </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="Q34" s="1"/>
+      <c r="AA34" s="40">
+        <v>2</v>
+      </c>
     </row>
     <row r="35" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
@@ -1807,6 +1830,9 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
+      <c r="AA46" s="40">
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="1:35" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A47" s="1">
@@ -7050,6 +7076,7 @@
     <hyperlink ref="B53" r:id="rId39" xr:uid="{E9872149-A9DB-264E-90DF-27490F0A05E9}"/>
     <hyperlink ref="B19" r:id="rId40" xr:uid="{B11CC4F6-040A-9441-A79D-83752EB074AE}"/>
     <hyperlink ref="B34" r:id="rId41" xr:uid="{B49926D5-FED1-B44A-B7BB-C47CB538FFD7}"/>
+    <hyperlink ref="B46" r:id="rId42" xr:uid="{EB885715-8124-8048-9149-97808A1FE6E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/worship songs.xlsx
+++ b/worship songs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/DATA/repo/worship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1483344-0C37-AF41-A7BE-5E112D82C00C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF951000-FA67-F049-AEAD-B59D0C2FF1EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4540" yWindow="660" windowWidth="18220" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-18580" yWindow="-3580" windowWidth="18220" windowHeight="18980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="song list" sheetId="1" r:id="rId1"/>
@@ -494,14 +494,14 @@
     <xf numFmtId="0" fontId="1" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -849,10 +849,10 @@
       </c>
     </row>
     <row r="3" spans="1:35" ht="13" x14ac:dyDescent="0.15">
-      <c r="A3" s="38" t="s">
+      <c r="A3" s="39" t="s">
         <v>34</v>
       </c>
-      <c r="B3" s="39"/>
+      <c r="B3" s="40"/>
       <c r="C3" s="32"/>
       <c r="D3" s="21"/>
       <c r="E3" s="16"/>
@@ -1337,7 +1337,7 @@
       <c r="W21" s="6">
         <v>1</v>
       </c>
-      <c r="AA21" s="40">
+      <c r="AA21" s="38">
         <v>1</v>
       </c>
     </row>
@@ -1371,7 +1371,7 @@
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="20" t="s">
+      <c r="B23" s="27" t="s">
         <v>8</v>
       </c>
       <c r="C23" s="1"/>
@@ -1388,7 +1388,7 @@
       <c r="T23" s="29">
         <v>3</v>
       </c>
-      <c r="AA23" s="40">
+      <c r="AA23" s="38">
         <v>3</v>
       </c>
     </row>
@@ -1431,7 +1431,7 @@
       <c r="V25" s="31">
         <v>4</v>
       </c>
-      <c r="AA25" s="40">
+      <c r="AA25" s="38">
         <v>4</v>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       <c r="F34" s="1"/>
       <c r="G34" s="1"/>
       <c r="Q34" s="1"/>
-      <c r="AA34" s="40">
+      <c r="AA34" s="38">
         <v>2</v>
       </c>
     </row>
@@ -1662,10 +1662,10 @@
       </c>
     </row>
     <row r="38" spans="1:35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="38" t="s">
+      <c r="A38" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B38" s="39"/>
+      <c r="B38" s="40"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1">
         <f>COUNTIF(F38:'song list'!END,"&lt;&gt;")</f>
@@ -1830,7 +1830,7 @@
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
-      <c r="AA46" s="40">
+      <c r="AA46" s="38">
         <v>5</v>
       </c>
     </row>
@@ -2154,10 +2154,10 @@
       <c r="F60" s="1"/>
     </row>
     <row r="61" spans="1:26" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="38" t="s">
+      <c r="A61" s="39" t="s">
         <v>36</v>
       </c>
-      <c r="B61" s="39"/>
+      <c r="B61" s="40"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1">
         <f>COUNTIF(F61:'song list'!END,"&lt;&gt;")</f>
@@ -7077,6 +7077,8 @@
     <hyperlink ref="B19" r:id="rId40" xr:uid="{B11CC4F6-040A-9441-A79D-83752EB074AE}"/>
     <hyperlink ref="B34" r:id="rId41" xr:uid="{B49926D5-FED1-B44A-B7BB-C47CB538FFD7}"/>
     <hyperlink ref="B46" r:id="rId42" xr:uid="{EB885715-8124-8048-9149-97808A1FE6E4}"/>
+    <hyperlink ref="B23" r:id="rId43" xr:uid="{88025645-3FD8-AA41-A03F-B14DEA5E4373}"/>
+    <hyperlink ref="B25" r:id="rId44" xr:uid="{17755188-4086-3544-BF71-977C7C068E72}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
